--- a/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmegoa\OneDrive - Minsur S.A\Escritorio\Carlos Mego\Proyecto Software\Módulo Inspecciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aplicaciones Web\EData\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Inspecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6D9556-0CA5-49B9-AF0A-A33AA463164A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569712BA-5368-491E-A890-D830887AFDF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,11 +24,11 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
+    <definedName name="LISTAFINAL">[1]Padrón!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Nivel Riesgo MA'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Nivel Riesgo SSO'!$A$1:$K$21</definedName>
-    <definedName name="LISTAFINAL">[1]Padrón!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="290">
   <si>
     <t>INSPECCIÓN</t>
   </si>
@@ -429,9 +429,6 @@
   </si>
   <si>
     <t>Acto/Condición de:</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Nivel de riesgo</t>
@@ -1576,7 +1573,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1795,9 +1792,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1812,9 +1806,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1825,14 +1816,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1883,15 +1868,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1916,317 +1892,38 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2256,6 +1953,293 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="1" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2646,7 +2630,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2967,7 +2951,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CA64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="19" customWidth="1"/>
     <col min="2" max="2" width="14" style="19" customWidth="1"/>
@@ -3014,7 +2998,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>40</v>
@@ -3022,981 +3006,981 @@
     </row>
     <row r="5" spans="1:79" s="10" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="11" t="str">
-        <f>IF(Inspección!$C24="MA","Tolerable","")</f>
-        <v/>
-      </c>
-      <c r="C5" s="12" t="str">
-        <f>IF(Inspección!$C24="MA","Alerta","")</f>
-        <v/>
-      </c>
-      <c r="D5" s="12" t="str">
-        <f>IF(Inspección!$C24="MA","No aceptable","")</f>
-        <v/>
-      </c>
-      <c r="E5" s="9" t="str">
-        <f>IF(Inspección!$C24="SSO","Bajo","")</f>
-        <v/>
-      </c>
-      <c r="F5" s="13" t="str">
-        <f>IF(Inspección!$C24="SSO","Medio","")</f>
-        <v/>
-      </c>
-      <c r="G5" s="13" t="str">
-        <f>IF(Inspección!$C24="SSO","Alto","")</f>
-        <v/>
+        <v>45</v>
+      </c>
+      <c r="B5" s="11" t="e">
+        <f>IF(Inspección!#REF!="MA","Tolerable","")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C5" s="12" t="e">
+        <f>IF(Inspección!#REF!="MA","Alerta","")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" s="12" t="e">
+        <f>IF(Inspección!#REF!="MA","No aceptable","")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="9" t="e">
+        <f>IF(Inspección!#REF!="SSO","Bajo","")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" s="13" t="e">
+        <f>IF(Inspección!#REF!="SSO","Medio","")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G5" s="13" t="e">
+        <f>IF(Inspección!#REF!="SSO","Alto","")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:79" s="16" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="S7" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q7" s="14" t="s">
+      <c r="T7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="T7" s="14" t="s">
+      <c r="U7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="W7" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="X7" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="X7" s="14" t="s">
+      <c r="Y7" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Z7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="AA7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AA7" s="14" t="s">
+      <c r="AB7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AB7" s="14" t="s">
+      <c r="AC7" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AC7" s="14" t="s">
+      <c r="AD7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AD7" s="14" t="s">
+      <c r="AF7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AE7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AG7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AH7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AH7" s="14" t="s">
+      <c r="AI7" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AI7" s="14" t="s">
+      <c r="AJ7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AJ7" s="14" t="s">
+      <c r="AK7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="AK7" s="14" t="s">
+      <c r="AL7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AL7" s="14" t="s">
+      <c r="AM7" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AM7" s="14" t="s">
+      <c r="AN7" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AN7" s="14" t="s">
+      <c r="AO7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP7" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="AO7" s="8" t="s">
+      <c r="AQ7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR7" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU7" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV7" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AW7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX7" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ7" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC7" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE7" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF7" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH7" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI7" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="AP7" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ7" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR7" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="AS7" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT7" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AU7" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="AV7" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AW7" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY7" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ7" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA7" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB7" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC7" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="BD7" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE7" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF7" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="BG7" s="15" t="s">
+      <c r="BJ7" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK7" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL7" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM7" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN7" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="BH7" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="BI7" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BJ7" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK7" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL7" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM7" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="BN7" s="14" t="s">
+      <c r="BO7" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP7" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ7" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="BS7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="BU7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BV7" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="BW7" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="BX7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="CA7" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="BO7" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP7" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ7" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR7" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="BS7" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="BT7" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="BU7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="BV7" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="BW7" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="BX7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="BY7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="BZ7" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="CA7" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:79" s="234" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="231" t="str">
-        <f>IF(Inspección!$C24="MA",$A$7,"")</f>
-        <v/>
-      </c>
-      <c r="B8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$B$7,"")</f>
-        <v/>
-      </c>
-      <c r="C8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$C$7,"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$D$7,"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$E$7,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$F$7,"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$G$7,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$H$7,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$I$7,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$J$7,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$K$7,"")</f>
-        <v/>
-      </c>
-      <c r="L8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$L$7,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$M$7,"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$N$7,"")</f>
-        <v/>
-      </c>
-      <c r="O8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$O$7,"")</f>
-        <v/>
-      </c>
-      <c r="P8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$P$7,"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$Q$7,"")</f>
-        <v/>
-      </c>
-      <c r="R8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$R$7,"")</f>
-        <v/>
-      </c>
-      <c r="S8" s="231" t="str">
-        <f>IF(Inspección!$C24="MA",$S$7,"")</f>
-        <v/>
-      </c>
-      <c r="T8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$T$7,"")</f>
-        <v/>
-      </c>
-      <c r="U8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$U$7,"")</f>
-        <v/>
-      </c>
-      <c r="V8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$V$7,"")</f>
-        <v/>
-      </c>
-      <c r="W8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$W$7,"")</f>
-        <v/>
-      </c>
-      <c r="X8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$X$7,"")</f>
-        <v/>
-      </c>
-      <c r="Y8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$Y$7,"")</f>
-        <v/>
-      </c>
-      <c r="Z8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$Z$7,"")</f>
-        <v/>
-      </c>
-      <c r="AA8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AA$7,"")</f>
-        <v/>
-      </c>
-      <c r="AB8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AB$7,"")</f>
-        <v/>
-      </c>
-      <c r="AC8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AC$7,"")</f>
-        <v/>
-      </c>
-      <c r="AD8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AD$7,"")</f>
-        <v/>
-      </c>
-      <c r="AE8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AE$7,"")</f>
-        <v/>
-      </c>
-      <c r="AF8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AF$7,"")</f>
-        <v/>
-      </c>
-      <c r="AG8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AG$7,"")</f>
-        <v/>
-      </c>
-      <c r="AH8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AH$7,"")</f>
-        <v/>
-      </c>
-      <c r="AI8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AI$7,"")</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AJ$7,"")</f>
-        <v/>
-      </c>
-      <c r="AK8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AK$7,"")</f>
-        <v/>
-      </c>
-      <c r="AL8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AL$7,"")</f>
-        <v/>
-      </c>
-      <c r="AM8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AM$7,"")</f>
-        <v/>
-      </c>
-      <c r="AN8" s="232" t="str">
-        <f>IF(Inspección!$C24="MA",$AN$7,"")</f>
-        <v/>
-      </c>
-      <c r="AO8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AO$7,"")</f>
-        <v/>
-      </c>
-      <c r="AP8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AP$7,"")</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AQ$7,"")</f>
-        <v/>
-      </c>
-      <c r="AR8" s="231" t="str">
-        <f>IF(Inspección!$C24="SSO",$AR$7,"")</f>
-        <v/>
-      </c>
-      <c r="AS8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AS$7,"")</f>
-        <v/>
-      </c>
-      <c r="AT8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AT$7,"")</f>
-        <v/>
-      </c>
-      <c r="AU8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AU$7,"")</f>
-        <v/>
-      </c>
-      <c r="AV8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AV$7,"")</f>
-        <v/>
-      </c>
-      <c r="AW8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AW$7,"")</f>
-        <v/>
-      </c>
-      <c r="AX8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AX$7,"")</f>
-        <v/>
-      </c>
-      <c r="AY8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AY$7,"")</f>
-        <v/>
-      </c>
-      <c r="AZ8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$AZ$7,"")</f>
-        <v/>
-      </c>
-      <c r="BA8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BA$7,"")</f>
-        <v/>
-      </c>
-      <c r="BB8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BB$7,"")</f>
-        <v/>
-      </c>
-      <c r="BC8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BC$7,"")</f>
-        <v/>
-      </c>
-      <c r="BD8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BD$7,"")</f>
-        <v/>
-      </c>
-      <c r="BE8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BE$7,"")</f>
-        <v/>
-      </c>
-      <c r="BF8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BF$7,"")</f>
-        <v/>
-      </c>
-      <c r="BG8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BG$7,"")</f>
-        <v/>
-      </c>
-      <c r="BH8" s="233" t="str">
-        <f>IF(Inspección!$C24="SSO",$BH$7,"")</f>
-        <v/>
-      </c>
-      <c r="BI8" s="231" t="str">
-        <f>IF(Inspección!$C24="SSO",$BI$7,"")</f>
-        <v/>
-      </c>
-      <c r="BJ8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BJ$7,"")</f>
-        <v/>
-      </c>
-      <c r="BK8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BK$7,"")</f>
-        <v/>
-      </c>
-      <c r="BL8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BL$7,"")</f>
-        <v/>
-      </c>
-      <c r="BM8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BM$7,"")</f>
-        <v/>
-      </c>
-      <c r="BN8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BN$7,"")</f>
-        <v/>
-      </c>
-      <c r="BO8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BO$7,"")</f>
-        <v/>
-      </c>
-      <c r="BP8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BP$7,"")</f>
-        <v/>
-      </c>
-      <c r="BQ8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BQ$7,"")</f>
-        <v/>
-      </c>
-      <c r="BR8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BR$7,"")</f>
-        <v/>
-      </c>
-      <c r="BS8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BS$7,"")</f>
-        <v/>
-      </c>
-      <c r="BT8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BT$7,"")</f>
-        <v/>
-      </c>
-      <c r="BU8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BU$7,"")</f>
-        <v/>
-      </c>
-      <c r="BV8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BV$7,"")</f>
-        <v/>
-      </c>
-      <c r="BW8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BW$7,"")</f>
-        <v/>
-      </c>
-      <c r="BX8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BX$7,"")</f>
-        <v/>
-      </c>
-      <c r="BY8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BY$7,"")</f>
-        <v/>
-      </c>
-      <c r="BZ8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$BZ$7,"")</f>
-        <v/>
-      </c>
-      <c r="CA8" s="232" t="str">
-        <f>IF(Inspección!$C24="SSO",$CA$7,"")</f>
-        <v/>
+    </row>
+    <row r="8" spans="1:79" s="134" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="131" t="e">
+        <f>IF(Inspección!#REF!="MA",$A$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$B$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$C$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$D$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$E$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$F$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$G$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$H$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$I$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$J$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$K$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$L$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$M$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$N$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$O$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$P$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$Q$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$R$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S8" s="131" t="e">
+        <f>IF(Inspección!#REF!="MA",$S$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$T$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$U$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$V$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$W$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$X$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$Y$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Z8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$Z$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AA$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AB$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AC$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AD8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AD$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AE8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AE$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AF8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AF$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AG8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AG$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AH8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AH$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AI8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AI$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AJ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AJ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AK8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AK$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AL8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AL$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AM8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AM$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AN8" s="132" t="e">
+        <f>IF(Inspección!#REF!="MA",$AN$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AO8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AO$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AP8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AP$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AQ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AQ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AR8" s="131" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AR$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AS8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AS$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AT8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AT$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AU8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AU$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AV8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AV$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AW8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AW$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AX8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AX$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AY8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AY$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AZ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$AZ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BA8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BA$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BB8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BB$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BC8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BC$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BD8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BD$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BE8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BE$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BF8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BF$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BG8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BG$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BH8" s="133" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BH$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BI8" s="131" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BI$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BJ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BJ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BK8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BK$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BL8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BL$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BM8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BM$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BN8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BN$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BO8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BO$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BP8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BP$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BQ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BQ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BR8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BR$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BS8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BS$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BT8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BT$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BU8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BU$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BV8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BV$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BW8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BW$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BX8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BX$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BY8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BY$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BZ8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$BZ$7,"")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CA8" s="132" t="e">
+        <f>IF(Inspección!#REF!="SSO",$CA$7,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:79" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:79" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="235" t="s">
-        <v>290</v>
-      </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="235" t="s">
+      <c r="A11" s="135" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" s="136"/>
+      <c r="C11" s="135" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="137" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="12" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="237" t="s">
+      <c r="B12" s="136"/>
+      <c r="C12" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="238" t="s">
+    </row>
+    <row r="13" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="137" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="13" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="237" t="s">
+      <c r="B13" s="136"/>
+      <c r="C13" s="138" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="236"/>
-      <c r="C13" s="238" t="s">
+    </row>
+    <row r="14" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="137" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="14" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="237" t="s">
+      <c r="B14" s="136"/>
+      <c r="C14" s="138" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="238" t="s">
+    </row>
+    <row r="15" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="137" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="15" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="237" t="s">
+      <c r="B15" s="136"/>
+      <c r="C15" s="138" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="238" t="s">
+    </row>
+    <row r="16" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="137" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="16" spans="1:79" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="237" t="s">
+      <c r="B16" s="136"/>
+      <c r="C16" s="138" t="s">
         <v>230</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="238" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="136" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="236" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="138" t="s">
         <v>232</v>
       </c>
-      <c r="B17" s="236"/>
-      <c r="C17" s="238" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="136" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="236" t="s">
+      <c r="B18" s="136"/>
+      <c r="C18" s="138" t="s">
         <v>234</v>
       </c>
-      <c r="B18" s="236"/>
-      <c r="C18" s="238" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A19" s="137" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="237" t="s">
+      <c r="B19" s="139"/>
+      <c r="C19" s="138" t="s">
         <v>236</v>
       </c>
-      <c r="B19" s="239"/>
-      <c r="C19" s="238" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="137" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="237" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="138" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="236"/>
-      <c r="C20" s="238" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="137" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="237" t="s">
+      <c r="B21" s="136"/>
+      <c r="C21" s="138" t="s">
         <v>240</v>
       </c>
-      <c r="B21" s="236"/>
-      <c r="C21" s="238" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="136" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="236" t="s">
+      <c r="B22" s="136"/>
+      <c r="C22" s="138" t="s">
         <v>242</v>
       </c>
-      <c r="B22" s="236"/>
-      <c r="C22" s="238" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="136" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="236" t="s">
+      <c r="B23" s="136"/>
+      <c r="C23" s="138" t="s">
         <v>244</v>
       </c>
-      <c r="B23" s="236"/>
-      <c r="C23" s="238" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="137" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="237" t="s">
+      <c r="B24" s="136"/>
+      <c r="C24" s="138" t="s">
         <v>246</v>
       </c>
-      <c r="B24" s="236"/>
-      <c r="C24" s="238" t="s">
+    </row>
+    <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="137" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="237" t="s">
+      <c r="B25" s="136"/>
+      <c r="C25" s="138" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="236"/>
-      <c r="C25" s="238" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="137" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="237" t="s">
+      <c r="B26" s="136"/>
+      <c r="C26" s="138" t="s">
         <v>250</v>
       </c>
-      <c r="B26" s="236"/>
-      <c r="C26" s="238" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="137" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="237" t="s">
+      <c r="B27" s="136"/>
+      <c r="C27" s="138" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="236"/>
-      <c r="C27" s="238" t="s">
+    </row>
+    <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="137" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="237" t="s">
+      <c r="B28" s="136"/>
+      <c r="C28" s="138" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="236"/>
-      <c r="C28" s="238" t="s">
+    </row>
+    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="136" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="236" t="s">
+      <c r="B29" s="136"/>
+      <c r="C29" s="138" t="s">
         <v>256</v>
       </c>
-      <c r="B29" s="236"/>
-      <c r="C29" s="238" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="136" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="236" t="s">
+      <c r="B30" s="136"/>
+      <c r="C30" s="138" t="s">
         <v>258</v>
       </c>
-      <c r="B30" s="236"/>
-      <c r="C30" s="238" t="s">
+    </row>
+    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="137" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="237" t="s">
+      <c r="B31" s="136"/>
+      <c r="C31" s="136"/>
+    </row>
+    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="136" t="s">
         <v>260</v>
       </c>
-      <c r="B31" s="236"/>
-      <c r="C31" s="236"/>
-    </row>
-    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="236" t="s">
+      <c r="B32" s="136"/>
+      <c r="C32" s="136"/>
+    </row>
+    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="137" t="s">
         <v>261</v>
       </c>
-      <c r="B32" s="236"/>
-      <c r="C32" s="236"/>
-    </row>
-    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="237" t="s">
+      <c r="B33" s="136"/>
+      <c r="C33" s="136"/>
+    </row>
+    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="137" t="s">
         <v>262</v>
       </c>
-      <c r="B33" s="236"/>
-      <c r="C33" s="236"/>
-    </row>
-    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="237" t="s">
+      <c r="B34" s="136"/>
+      <c r="C34" s="136"/>
+    </row>
+    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="136" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="236"/>
-      <c r="C34" s="236"/>
-    </row>
-    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="236" t="s">
+      <c r="B35" s="136"/>
+      <c r="C35" s="136"/>
+    </row>
+    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="136" t="s">
         <v>264</v>
       </c>
-      <c r="B35" s="236"/>
-      <c r="C35" s="236"/>
-    </row>
-    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="236" t="s">
+      <c r="B36" s="136"/>
+      <c r="C36" s="136"/>
+    </row>
+    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="137" t="s">
         <v>265</v>
       </c>
-      <c r="B36" s="236"/>
-      <c r="C36" s="236"/>
-    </row>
-    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="237" t="s">
+      <c r="B37" s="136"/>
+      <c r="C37" s="136"/>
+    </row>
+    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="B37" s="236"/>
-      <c r="C37" s="236"/>
-    </row>
-    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="237" t="s">
+      <c r="B38" s="136"/>
+      <c r="C38" s="136"/>
+    </row>
+    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="140" t="s">
         <v>267</v>
       </c>
-      <c r="B38" s="236"/>
-      <c r="C38" s="236"/>
-    </row>
-    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="240" t="s">
+      <c r="B39" s="136"/>
+      <c r="C39" s="136"/>
+    </row>
+    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="137" t="s">
         <v>268</v>
       </c>
-      <c r="B39" s="236"/>
-      <c r="C39" s="236"/>
-    </row>
-    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="237" t="s">
+      <c r="B40" s="136"/>
+      <c r="C40" s="136"/>
+    </row>
+    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="137" t="s">
         <v>269</v>
       </c>
-      <c r="B40" s="236"/>
-      <c r="C40" s="236"/>
-    </row>
-    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="237" t="s">
+      <c r="B41" s="136"/>
+      <c r="C41" s="136"/>
+    </row>
+    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="137" t="s">
         <v>270</v>
       </c>
-      <c r="B41" s="236"/>
-      <c r="C41" s="236"/>
-    </row>
-    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="237" t="s">
+      <c r="B42" s="136"/>
+      <c r="C42" s="136"/>
+    </row>
+    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="136" t="s">
         <v>271</v>
       </c>
-      <c r="B42" s="236"/>
-      <c r="C42" s="236"/>
-    </row>
-    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="236" t="s">
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
+    </row>
+    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="136" t="s">
         <v>272</v>
       </c>
-      <c r="B43" s="236"/>
-      <c r="C43" s="236"/>
-    </row>
-    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="236" t="s">
+      <c r="B44" s="136"/>
+      <c r="C44" s="136"/>
+    </row>
+    <row r="45" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="137" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="236"/>
-      <c r="C44" s="236"/>
-    </row>
-    <row r="45" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="237" t="s">
+      <c r="B45" s="136"/>
+      <c r="C45" s="136"/>
+    </row>
+    <row r="46" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="137" t="s">
         <v>274</v>
       </c>
-      <c r="B45" s="236"/>
-      <c r="C45" s="236"/>
-    </row>
-    <row r="46" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="237" t="s">
+      <c r="B46" s="136"/>
+      <c r="C46" s="136"/>
+    </row>
+    <row r="47" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="137" t="s">
         <v>275</v>
       </c>
-      <c r="B46" s="236"/>
-      <c r="C46" s="236"/>
-    </row>
-    <row r="47" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="237" t="s">
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+    </row>
+    <row r="48" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="B47" s="236"/>
-      <c r="C47" s="236"/>
-    </row>
-    <row r="48" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="237" t="s">
+      <c r="B48" s="136"/>
+      <c r="C48" s="136"/>
+    </row>
+    <row r="49" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="136" t="s">
         <v>277</v>
       </c>
-      <c r="B48" s="236"/>
-      <c r="C48" s="236"/>
-    </row>
-    <row r="49" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="236" t="s">
+      <c r="B49" s="136"/>
+      <c r="C49" s="136"/>
+    </row>
+    <row r="50" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="137" t="s">
         <v>278</v>
       </c>
-      <c r="B49" s="236"/>
-      <c r="C49" s="236"/>
-    </row>
-    <row r="50" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="237" t="s">
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+    </row>
+    <row r="51" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="136" t="s">
         <v>279</v>
       </c>
-      <c r="B50" s="236"/>
-      <c r="C50" s="236"/>
-    </row>
-    <row r="51" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="236" t="s">
+      <c r="B51" s="136"/>
+      <c r="C51" s="136"/>
+    </row>
+    <row r="52" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="B51" s="236"/>
-      <c r="C51" s="236"/>
-    </row>
-    <row r="52" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="237" t="s">
+      <c r="B52" s="136"/>
+      <c r="C52" s="136"/>
+    </row>
+    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="136" t="s">
         <v>281</v>
       </c>
-      <c r="B52" s="236"/>
-      <c r="C52" s="236"/>
-    </row>
-    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="236" t="s">
+      <c r="B53" s="136"/>
+      <c r="C53" s="136"/>
+    </row>
+    <row r="54" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="137" t="s">
         <v>282</v>
       </c>
-      <c r="B53" s="236"/>
-      <c r="C53" s="236"/>
-    </row>
-    <row r="54" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="237" t="s">
+      <c r="B54" s="136"/>
+      <c r="C54" s="136"/>
+    </row>
+    <row r="55" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="137" t="s">
         <v>283</v>
       </c>
-      <c r="B54" s="236"/>
-      <c r="C54" s="236"/>
-    </row>
-    <row r="55" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="237" t="s">
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+    </row>
+    <row r="56" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="137" t="s">
         <v>284</v>
       </c>
-      <c r="B55" s="236"/>
-      <c r="C55" s="236"/>
-    </row>
-    <row r="56" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="237" t="s">
+      <c r="B56" s="136"/>
+      <c r="C56" s="136"/>
+    </row>
+    <row r="57" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="136" t="s">
         <v>285</v>
       </c>
-      <c r="B56" s="236"/>
-      <c r="C56" s="236"/>
-    </row>
-    <row r="57" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="236" t="s">
+      <c r="B57" s="136"/>
+      <c r="C57" s="136"/>
+    </row>
+    <row r="58" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="136" t="s">
         <v>286</v>
       </c>
-      <c r="B57" s="236"/>
-      <c r="C57" s="236"/>
-    </row>
-    <row r="58" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="236" t="s">
+      <c r="B58" s="136"/>
+      <c r="C58" s="136"/>
+    </row>
+    <row r="59" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="137" t="s">
         <v>287</v>
       </c>
-      <c r="B58" s="236"/>
-      <c r="C58" s="236"/>
-    </row>
-    <row r="59" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="237" t="s">
+      <c r="B59" s="136"/>
+      <c r="C59" s="136"/>
+    </row>
+    <row r="60" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="136" t="s">
         <v>288</v>
       </c>
-      <c r="B59" s="236"/>
-      <c r="C59" s="236"/>
-    </row>
-    <row r="60" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="236" t="s">
-        <v>289</v>
-      </c>
-      <c r="B60" s="236"/>
-      <c r="C60" s="236"/>
+      <c r="B60" s="136"/>
+      <c r="C60" s="136"/>
     </row>
     <row r="61" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61"/>
@@ -4028,8 +4012,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF403"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="78" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" style="78" customWidth="1"/>
@@ -4067,1075 +4051,3088 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="173"/>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="209" t="s">
+      <c r="A1" s="189"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="169" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="210"/>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="210"/>
-      <c r="Y1" s="210"/>
-      <c r="Z1" s="210"/>
-      <c r="AA1" s="211"/>
-      <c r="AB1" s="200"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="201"/>
-      <c r="AE1" s="202"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
+      <c r="Z1" s="170"/>
+      <c r="AA1" s="171"/>
+      <c r="AB1" s="160"/>
+      <c r="AC1" s="161"/>
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="162"/>
     </row>
     <row r="2" spans="1:32" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="176"/>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="178"/>
+      <c r="A2" s="192"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="194"/>
       <c r="H2" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="212" t="s">
+      <c r="I2" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
-      <c r="N2" s="212"/>
-      <c r="O2" s="213"/>
-      <c r="P2" s="186" t="s">
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="184"/>
-      <c r="R2" s="183">
+      <c r="Q2" s="144"/>
+      <c r="R2" s="202">
         <v>43831</v>
       </c>
-      <c r="S2" s="184"/>
-      <c r="T2" s="184"/>
-      <c r="U2" s="184"/>
-      <c r="V2" s="185"/>
-      <c r="W2" s="80" t="s">
+      <c r="S2" s="202"/>
+      <c r="T2" s="202"/>
+      <c r="U2" s="202"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="X2" s="193" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y2" s="194"/>
-      <c r="Z2" s="194"/>
-      <c r="AA2" s="195"/>
-      <c r="AB2" s="203"/>
-      <c r="AC2" s="204"/>
-      <c r="AD2" s="204"/>
-      <c r="AE2" s="205"/>
+      <c r="X2" s="152" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="165"/>
     </row>
     <row r="3" spans="1:32" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="179"/>
-      <c r="B3" s="180"/>
-      <c r="C3" s="180"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="181"/>
+      <c r="A3" s="195"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="197"/>
       <c r="H3" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="212" t="s">
+      <c r="I3" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="212"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214" t="s">
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
+      <c r="P3" s="174" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="215"/>
-      <c r="R3" s="164">
+      <c r="Q3" s="175"/>
+      <c r="R3" s="179">
         <v>1</v>
       </c>
-      <c r="S3" s="164"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="164"/>
-      <c r="V3" s="165"/>
-      <c r="W3" s="191" t="s">
+      <c r="S3" s="179"/>
+      <c r="T3" s="179"/>
+      <c r="U3" s="179"/>
+      <c r="V3" s="180"/>
+      <c r="W3" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="190">
+      <c r="X3" s="151"/>
+      <c r="Y3" s="148">
         <v>43800</v>
       </c>
-      <c r="Z3" s="146"/>
-      <c r="AA3" s="147"/>
-      <c r="AB3" s="206"/>
-      <c r="AC3" s="207"/>
-      <c r="AD3" s="207"/>
-      <c r="AE3" s="208"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="84"/>
-      <c r="U4" s="84"/>
-      <c r="V4" s="84"/>
-      <c r="W4" s="84"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="84"/>
-      <c r="Z4" s="84"/>
-      <c r="AA4" s="81"/>
-      <c r="AB4" s="81"/>
-      <c r="AC4" s="81"/>
-      <c r="AD4" s="86"/>
-      <c r="AE4" s="86"/>
+      <c r="Z3" s="148"/>
+      <c r="AA3" s="149"/>
+      <c r="AB3" s="166"/>
+      <c r="AC3" s="167"/>
+      <c r="AD3" s="167"/>
+      <c r="AE3" s="168"/>
+    </row>
+    <row r="4" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="84"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="130"/>
+      <c r="AE4" s="130"/>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="187" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="172"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="172"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="172"/>
-      <c r="P5" s="172"/>
-      <c r="Q5" s="172"/>
-      <c r="R5" s="172"/>
-      <c r="S5" s="172"/>
-      <c r="T5" s="172"/>
-      <c r="U5" s="172"/>
-      <c r="V5" s="172"/>
-      <c r="W5" s="172"/>
-      <c r="X5" s="172"/>
-      <c r="Y5" s="172"/>
-      <c r="Z5" s="172"/>
-      <c r="AA5" s="172"/>
-      <c r="AB5" s="172"/>
-      <c r="AC5" s="172"/>
-      <c r="AD5" s="172"/>
-      <c r="AE5" s="182"/>
-    </row>
-    <row r="6" spans="1:32" s="90" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="87"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="88"/>
-      <c r="T6" s="88"/>
-      <c r="U6" s="88"/>
-      <c r="V6" s="88"/>
-      <c r="W6" s="88"/>
-      <c r="X6" s="88"/>
-      <c r="Y6" s="88"/>
-      <c r="Z6" s="88"/>
-      <c r="AA6" s="88"/>
-      <c r="AB6" s="88"/>
-      <c r="AC6" s="88"/>
-      <c r="AD6" s="88"/>
-      <c r="AE6" s="89"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
+      <c r="L5" s="188"/>
+      <c r="M5" s="188"/>
+      <c r="N5" s="188"/>
+      <c r="O5" s="188"/>
+      <c r="P5" s="188"/>
+      <c r="Q5" s="188"/>
+      <c r="R5" s="188"/>
+      <c r="S5" s="188"/>
+      <c r="T5" s="188"/>
+      <c r="U5" s="188"/>
+      <c r="V5" s="188"/>
+      <c r="W5" s="188"/>
+      <c r="X5" s="188"/>
+      <c r="Y5" s="188"/>
+      <c r="Z5" s="188"/>
+      <c r="AA5" s="188"/>
+      <c r="AB5" s="188"/>
+      <c r="AC5" s="188"/>
+      <c r="AD5" s="188"/>
+      <c r="AE5" s="198"/>
+    </row>
+    <row r="6" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="86"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="86"/>
+      <c r="T6" s="86"/>
+      <c r="U6" s="86"/>
+      <c r="V6" s="86"/>
+      <c r="W6" s="86"/>
+      <c r="X6" s="86"/>
+      <c r="Y6" s="86"/>
+      <c r="Z6" s="86"/>
+      <c r="AA6" s="86"/>
+      <c r="AB6" s="86"/>
+      <c r="AC6" s="86"/>
+      <c r="AD6" s="86"/>
+      <c r="AE6" s="87"/>
     </row>
     <row r="7" spans="1:32" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="91"/>
-      <c r="B7" s="133" t="s">
+      <c r="A7" s="89"/>
+      <c r="B7" s="158" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="216" t="s">
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="176" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="217"/>
-      <c r="J7" s="218"/>
-      <c r="K7" s="92" t="s">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="216">
+      <c r="L7" s="176">
         <v>20508972734</v>
       </c>
-      <c r="M7" s="217"/>
-      <c r="N7" s="218"/>
-      <c r="O7" s="133" t="s">
+      <c r="M7" s="177"/>
+      <c r="N7" s="178"/>
+      <c r="O7" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="199"/>
-      <c r="R7" s="196" t="s">
+      <c r="P7" s="158"/>
+      <c r="Q7" s="159"/>
+      <c r="R7" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="S7" s="197"/>
-      <c r="T7" s="197"/>
-      <c r="U7" s="197"/>
-      <c r="V7" s="198"/>
-      <c r="W7" s="93"/>
-      <c r="X7" s="94" t="s">
+      <c r="S7" s="155"/>
+      <c r="T7" s="155"/>
+      <c r="U7" s="155"/>
+      <c r="V7" s="156"/>
+      <c r="W7" s="90"/>
+      <c r="X7" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" s="196" t="s">
+      <c r="Y7" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="Z7" s="197"/>
-      <c r="AA7" s="197"/>
-      <c r="AB7" s="197"/>
-      <c r="AC7" s="197"/>
-      <c r="AD7" s="198"/>
-      <c r="AE7" s="95"/>
+      <c r="Z7" s="155"/>
+      <c r="AA7" s="155"/>
+      <c r="AB7" s="155"/>
+      <c r="AC7" s="155"/>
+      <c r="AD7" s="156"/>
+      <c r="AE7" s="91"/>
     </row>
     <row r="8" spans="1:32" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="96"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="97"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="97"/>
-      <c r="O8" s="97"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="97"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="99"/>
-      <c r="U8" s="99"/>
-      <c r="V8" s="99"/>
-      <c r="W8" s="99"/>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="99"/>
-      <c r="AB8" s="99"/>
-      <c r="AC8" s="99"/>
-      <c r="AD8" s="100"/>
-      <c r="AE8" s="101"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B9" s="102"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="103"/>
-      <c r="AC9" s="103"/>
-      <c r="AD9" s="103"/>
-      <c r="AE9" s="103"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
+      <c r="P8" s="93"/>
+      <c r="Q8" s="93"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+      <c r="T8" s="95"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="95"/>
+      <c r="W8" s="95"/>
+      <c r="X8" s="93"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="96"/>
+      <c r="AE8" s="97"/>
+    </row>
+    <row r="9" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="98"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="171" t="s">
+      <c r="A10" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
-      <c r="D10" s="172"/>
-      <c r="E10" s="172"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="172"/>
-      <c r="H10" s="172"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="172"/>
-      <c r="K10" s="172"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="172"/>
-      <c r="O10" s="172"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="172"/>
-      <c r="R10" s="172"/>
-      <c r="S10" s="172"/>
-      <c r="T10" s="172"/>
-      <c r="U10" s="172"/>
-      <c r="V10" s="172"/>
-      <c r="W10" s="172"/>
-      <c r="X10" s="172"/>
-      <c r="Y10" s="172"/>
-      <c r="Z10" s="172"/>
-      <c r="AA10" s="172"/>
-      <c r="AB10" s="172"/>
-      <c r="AC10" s="172"/>
-      <c r="AD10" s="172"/>
-      <c r="AE10" s="182"/>
-    </row>
-    <row r="11" spans="1:32" s="90" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="107"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="107"/>
-      <c r="Q11" s="107"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="89"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="188"/>
+      <c r="G10" s="188"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="188"/>
+      <c r="L10" s="188"/>
+      <c r="M10" s="188"/>
+      <c r="N10" s="188"/>
+      <c r="O10" s="188"/>
+      <c r="P10" s="188"/>
+      <c r="Q10" s="188"/>
+      <c r="R10" s="188"/>
+      <c r="S10" s="188"/>
+      <c r="T10" s="188"/>
+      <c r="U10" s="188"/>
+      <c r="V10" s="188"/>
+      <c r="W10" s="188"/>
+      <c r="X10" s="188"/>
+      <c r="Y10" s="188"/>
+      <c r="Z10" s="188"/>
+      <c r="AA10" s="188"/>
+      <c r="AB10" s="188"/>
+      <c r="AC10" s="188"/>
+      <c r="AD10" s="188"/>
+      <c r="AE10" s="198"/>
+    </row>
+    <row r="11" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="86"/>
+      <c r="Z11" s="86"/>
+      <c r="AA11" s="86"/>
+      <c r="AB11" s="86"/>
+      <c r="AC11" s="86"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="87"/>
     </row>
     <row r="12" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="140" t="s">
+      <c r="A12" s="89"/>
+      <c r="B12" s="215" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="215"/>
+      <c r="D12" s="215"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="215"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="212"/>
+      <c r="M12" s="222" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="206"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="199"/>
+      <c r="Q12" s="200"/>
+      <c r="R12" s="200"/>
+      <c r="S12" s="200"/>
+      <c r="T12" s="201"/>
+      <c r="U12" s="145" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="144"/>
-      <c r="M12" s="139" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" s="139"/>
-      <c r="O12" s="139"/>
-      <c r="P12" s="155"/>
-      <c r="Q12" s="156"/>
-      <c r="R12" s="156"/>
-      <c r="S12" s="156"/>
-      <c r="T12" s="157"/>
-      <c r="U12" s="187" t="s">
-        <v>219</v>
-      </c>
-      <c r="V12" s="188"/>
-      <c r="W12" s="188"/>
-      <c r="X12" s="189"/>
-      <c r="Y12" s="145"/>
-      <c r="Z12" s="146"/>
-      <c r="AA12" s="146"/>
-      <c r="AB12" s="146"/>
-      <c r="AC12" s="146"/>
-      <c r="AD12" s="147"/>
-      <c r="AE12" s="108"/>
+      <c r="V12" s="146"/>
+      <c r="W12" s="146"/>
+      <c r="X12" s="147"/>
+      <c r="Y12" s="235"/>
+      <c r="Z12" s="236"/>
+      <c r="AA12" s="236"/>
+      <c r="AB12" s="236"/>
+      <c r="AC12" s="236"/>
+      <c r="AD12" s="237"/>
+      <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="110"/>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="110"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="111"/>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
-      <c r="X13" s="112"/>
-      <c r="Y13" s="110"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="110"/>
-      <c r="AB13" s="110"/>
-      <c r="AC13" s="110"/>
-      <c r="AD13" s="110"/>
-      <c r="AE13" s="113"/>
+      <c r="A13" s="89"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="106"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="107"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="107"/>
+      <c r="V13" s="107"/>
+      <c r="W13" s="107"/>
+      <c r="X13" s="108"/>
+      <c r="Y13" s="106"/>
+      <c r="Z13" s="106"/>
+      <c r="AA13" s="106"/>
+      <c r="AB13" s="106"/>
+      <c r="AC13" s="106"/>
+      <c r="AD13" s="106"/>
+      <c r="AE13" s="109"/>
     </row>
     <row r="14" spans="1:32" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="91"/>
-      <c r="B14" s="148" t="s">
+      <c r="A14" s="89"/>
+      <c r="B14" s="204" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="145"/>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="114" t="s">
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="205"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="218"/>
+      <c r="J14" s="218"/>
+      <c r="K14" s="218"/>
+      <c r="L14" s="214"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="115" t="s">
+      <c r="P14" s="211"/>
+      <c r="Q14" s="212"/>
+      <c r="R14" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="S14" s="138"/>
-      <c r="T14" s="138"/>
-      <c r="U14" s="116"/>
-      <c r="V14" s="139" t="s">
+      <c r="S14" s="235"/>
+      <c r="T14" s="237"/>
+      <c r="U14" s="125"/>
+      <c r="V14" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="W14" s="139"/>
-      <c r="X14" s="139"/>
-      <c r="Y14" s="161"/>
-      <c r="Z14" s="162"/>
-      <c r="AA14" s="162"/>
-      <c r="AB14" s="162"/>
-      <c r="AC14" s="162"/>
-      <c r="AD14" s="163"/>
-      <c r="AE14" s="117"/>
-      <c r="AF14" s="118"/>
+      <c r="W14" s="206"/>
+      <c r="X14" s="207"/>
+      <c r="Y14" s="219"/>
+      <c r="Z14" s="220"/>
+      <c r="AA14" s="220"/>
+      <c r="AB14" s="220"/>
+      <c r="AC14" s="220"/>
+      <c r="AD14" s="221"/>
+      <c r="AE14" s="110"/>
+      <c r="AF14" s="111"/>
     </row>
     <row r="15" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="91"/>
-      <c r="B15" s="109"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="119"/>
-      <c r="M15" s="119"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="119"/>
-      <c r="Q15" s="119"/>
-      <c r="R15" s="119"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="119"/>
-      <c r="Z15" s="119"/>
-      <c r="AA15" s="119"/>
-      <c r="AB15" s="119"/>
-      <c r="AC15" s="119"/>
-      <c r="AD15" s="119"/>
-      <c r="AE15" s="120"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="107"/>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107"/>
+      <c r="V15" s="107"/>
+      <c r="W15" s="107"/>
+      <c r="X15" s="106"/>
+      <c r="Y15" s="112"/>
+      <c r="Z15" s="112"/>
+      <c r="AA15" s="112"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="112"/>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="113"/>
     </row>
     <row r="16" spans="1:32" ht="49.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="91"/>
-      <c r="B16" s="148" t="s">
+      <c r="A16" s="89"/>
+      <c r="B16" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="155"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="156"/>
-      <c r="L16" s="157"/>
-      <c r="M16" s="134" t="s">
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="205"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="200"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="200"/>
+      <c r="L16" s="201"/>
+      <c r="M16" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="135"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="121"/>
-      <c r="Q16" s="121"/>
-      <c r="R16" s="121"/>
-      <c r="S16" s="139" t="s">
+      <c r="N16" s="209"/>
+      <c r="O16" s="210"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="139"/>
-      <c r="X16" s="139"/>
-      <c r="Y16" s="152"/>
-      <c r="Z16" s="153"/>
-      <c r="AA16" s="153"/>
-      <c r="AB16" s="154"/>
-      <c r="AC16" s="134" t="s">
+      <c r="T16" s="206"/>
+      <c r="U16" s="206"/>
+      <c r="V16" s="206"/>
+      <c r="W16" s="206"/>
+      <c r="X16" s="207"/>
+      <c r="Y16" s="199"/>
+      <c r="Z16" s="200"/>
+      <c r="AA16" s="200"/>
+      <c r="AB16" s="201"/>
+      <c r="AC16" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="AD16" s="136"/>
-      <c r="AE16" s="122"/>
+      <c r="AD16" s="210"/>
+      <c r="AE16" s="115"/>
     </row>
     <row r="17" spans="1:31" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="91"/>
-      <c r="B17" s="109"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="111"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="111"/>
-      <c r="W17" s="111"/>
-      <c r="X17" s="110"/>
-      <c r="Y17" s="110"/>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="110"/>
-      <c r="AB17" s="110"/>
-      <c r="AC17" s="110"/>
-      <c r="AD17" s="110"/>
-      <c r="AE17" s="113"/>
+      <c r="A17" s="89"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="106"/>
+      <c r="O17" s="106"/>
+      <c r="P17" s="106"/>
+      <c r="Q17" s="106"/>
+      <c r="R17" s="106"/>
+      <c r="S17" s="107"/>
+      <c r="T17" s="107"/>
+      <c r="U17" s="107"/>
+      <c r="V17" s="107"/>
+      <c r="W17" s="107"/>
+      <c r="X17" s="106"/>
+      <c r="Y17" s="106"/>
+      <c r="Z17" s="106"/>
+      <c r="AA17" s="106"/>
+      <c r="AB17" s="106"/>
+      <c r="AC17" s="106"/>
+      <c r="AD17" s="106"/>
+      <c r="AE17" s="109"/>
     </row>
     <row r="18" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="91"/>
-      <c r="B18" s="148" t="s">
+      <c r="A18" s="89"/>
+      <c r="B18" s="204" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="148"/>
-      <c r="D18" s="148"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="155"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="156"/>
-      <c r="L18" s="156"/>
-      <c r="M18" s="156"/>
-      <c r="N18" s="156"/>
-      <c r="O18" s="156"/>
-      <c r="P18" s="156"/>
-      <c r="Q18" s="156"/>
-      <c r="R18" s="156"/>
-      <c r="S18" s="156"/>
-      <c r="T18" s="156"/>
-      <c r="U18" s="156"/>
-      <c r="V18" s="156"/>
-      <c r="W18" s="156"/>
-      <c r="X18" s="156"/>
-      <c r="Y18" s="156"/>
-      <c r="Z18" s="156"/>
-      <c r="AA18" s="156"/>
-      <c r="AB18" s="156"/>
-      <c r="AC18" s="156"/>
-      <c r="AD18" s="157"/>
-      <c r="AE18" s="123"/>
+      <c r="C18" s="204"/>
+      <c r="D18" s="204"/>
+      <c r="E18" s="204"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="205"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="200"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="200"/>
+      <c r="N18" s="200"/>
+      <c r="O18" s="200"/>
+      <c r="P18" s="200"/>
+      <c r="Q18" s="200"/>
+      <c r="R18" s="200"/>
+      <c r="S18" s="200"/>
+      <c r="T18" s="200"/>
+      <c r="U18" s="200"/>
+      <c r="V18" s="200"/>
+      <c r="W18" s="200"/>
+      <c r="X18" s="200"/>
+      <c r="Y18" s="200"/>
+      <c r="Z18" s="200"/>
+      <c r="AA18" s="200"/>
+      <c r="AB18" s="200"/>
+      <c r="AC18" s="200"/>
+      <c r="AD18" s="201"/>
+      <c r="AE18" s="116"/>
     </row>
     <row r="19" spans="1:31" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="96"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
-      <c r="P19" s="125"/>
-      <c r="Q19" s="125"/>
-      <c r="R19" s="125"/>
-      <c r="S19" s="125"/>
-      <c r="T19" s="125"/>
-      <c r="U19" s="125"/>
-      <c r="V19" s="125"/>
-      <c r="W19" s="125"/>
-      <c r="X19" s="125"/>
-      <c r="Y19" s="125"/>
-      <c r="Z19" s="125"/>
-      <c r="AA19" s="125"/>
-      <c r="AB19" s="125"/>
-      <c r="AC19" s="125"/>
-      <c r="AD19" s="125"/>
-      <c r="AE19" s="126"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="151"/>
-      <c r="K20" s="151"/>
-      <c r="L20" s="151"/>
-      <c r="M20" s="151"/>
-      <c r="N20" s="151"/>
-      <c r="O20" s="151"/>
-      <c r="P20" s="151"/>
-      <c r="Q20" s="151"/>
-      <c r="R20" s="151"/>
-      <c r="S20" s="151"/>
-      <c r="T20" s="151"/>
-      <c r="U20" s="151"/>
-      <c r="V20" s="151"/>
-      <c r="W20" s="151"/>
-      <c r="X20" s="151"/>
-      <c r="Y20" s="151"/>
-      <c r="Z20" s="151"/>
-      <c r="AA20" s="151"/>
-      <c r="AB20" s="151"/>
-      <c r="AC20" s="151"/>
-      <c r="AD20" s="151"/>
-      <c r="AE20" s="151"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="118"/>
+      <c r="U19" s="118"/>
+      <c r="V19" s="118"/>
+      <c r="W19" s="118"/>
+      <c r="X19" s="118"/>
+      <c r="Y19" s="118"/>
+      <c r="Z19" s="118"/>
+      <c r="AA19" s="118"/>
+      <c r="AB19" s="118"/>
+      <c r="AC19" s="118"/>
+      <c r="AD19" s="118"/>
+      <c r="AE19" s="119"/>
+    </row>
+    <row r="20" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="111"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="200"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="200"/>
+      <c r="I20" s="200"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="200"/>
+      <c r="L20" s="200"/>
+      <c r="M20" s="200"/>
+      <c r="N20" s="200"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="200"/>
+      <c r="Q20" s="200"/>
+      <c r="R20" s="200"/>
+      <c r="S20" s="200"/>
+      <c r="T20" s="200"/>
+      <c r="U20" s="200"/>
+      <c r="V20" s="200"/>
+      <c r="W20" s="200"/>
+      <c r="X20" s="200"/>
+      <c r="Y20" s="200"/>
+      <c r="Z20" s="200"/>
+      <c r="AA20" s="200"/>
+      <c r="AB20" s="200"/>
+      <c r="AC20" s="200"/>
+      <c r="AD20" s="200"/>
+      <c r="AE20" s="200"/>
     </row>
     <row r="21" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="171" t="s">
+      <c r="A21" s="187" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="172"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="172"/>
-      <c r="G21" s="172"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="128"/>
-      <c r="N21" s="128"/>
-      <c r="O21" s="128"/>
-      <c r="P21" s="128"/>
-      <c r="Q21" s="128"/>
-      <c r="R21" s="128"/>
-      <c r="S21" s="128"/>
-      <c r="T21" s="128"/>
-      <c r="U21" s="128"/>
-      <c r="V21" s="128"/>
-      <c r="W21" s="128"/>
-      <c r="X21" s="128"/>
-      <c r="Y21" s="128"/>
-      <c r="Z21" s="128"/>
-      <c r="AA21" s="128"/>
-      <c r="AB21" s="128"/>
-      <c r="AC21" s="128"/>
-      <c r="AD21" s="128"/>
-      <c r="AE21" s="129"/>
+      <c r="B21" s="188"/>
+      <c r="C21" s="188"/>
+      <c r="D21" s="188"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="120"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="120"/>
+      <c r="S21" s="120"/>
+      <c r="T21" s="120"/>
+      <c r="U21" s="120"/>
+      <c r="V21" s="120"/>
+      <c r="W21" s="120"/>
+      <c r="X21" s="120"/>
+      <c r="Y21" s="120"/>
+      <c r="Z21" s="120"/>
+      <c r="AA21" s="120"/>
+      <c r="AB21" s="120"/>
+      <c r="AC21" s="120"/>
+      <c r="AD21" s="120"/>
+      <c r="AE21" s="121"/>
     </row>
     <row r="22" spans="1:31" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="166"/>
-      <c r="B22" s="167"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="167"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="167"/>
-      <c r="K22" s="167"/>
-      <c r="L22" s="167"/>
-      <c r="M22" s="167"/>
-      <c r="N22" s="167"/>
-      <c r="O22" s="167"/>
-      <c r="P22" s="167"/>
-      <c r="Q22" s="167"/>
-      <c r="R22" s="167"/>
-      <c r="S22" s="167"/>
-      <c r="T22" s="167"/>
-      <c r="U22" s="167"/>
-      <c r="V22" s="167"/>
-      <c r="W22" s="167"/>
-      <c r="X22" s="167"/>
-      <c r="Y22" s="167"/>
-      <c r="Z22" s="167"/>
-      <c r="AA22" s="167"/>
-      <c r="AB22" s="167"/>
-      <c r="AC22" s="167"/>
-      <c r="AD22" s="167"/>
-      <c r="AE22" s="168"/>
-    </row>
-    <row r="23" spans="1:31" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="158" t="s">
+      <c r="A22" s="181"/>
+      <c r="B22" s="182"/>
+      <c r="C22" s="182"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="182"/>
+      <c r="F22" s="182"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="182"/>
+      <c r="I22" s="182"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="182"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="182"/>
+      <c r="Q22" s="182"/>
+      <c r="R22" s="182"/>
+      <c r="S22" s="182"/>
+      <c r="T22" s="182"/>
+      <c r="U22" s="182"/>
+      <c r="V22" s="182"/>
+      <c r="W22" s="182"/>
+      <c r="X22" s="182"/>
+      <c r="Y22" s="182"/>
+      <c r="Z22" s="182"/>
+      <c r="AA22" s="182"/>
+      <c r="AB22" s="182"/>
+      <c r="AC22" s="182"/>
+      <c r="AD22" s="182"/>
+      <c r="AE22" s="183"/>
+    </row>
+    <row r="23" spans="1:31" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="160"/>
-      <c r="C23" s="130" t="s">
+      <c r="B23" s="186"/>
+      <c r="C23" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="158" t="s">
+      <c r="D23" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="159"/>
-      <c r="F23" s="159"/>
-      <c r="G23" s="159"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="160"/>
-      <c r="J23" s="158" t="s">
+      <c r="E23" s="185"/>
+      <c r="F23" s="185"/>
+      <c r="G23" s="185"/>
+      <c r="H23" s="185"/>
+      <c r="I23" s="186"/>
+      <c r="J23" s="184" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
-      <c r="M23" s="159"/>
-      <c r="N23" s="159"/>
-      <c r="O23" s="158" t="s">
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="185"/>
+      <c r="N23" s="186"/>
+      <c r="O23" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="159"/>
-      <c r="Q23" s="160"/>
-      <c r="R23" s="130" t="s">
+      <c r="P23" s="185"/>
+      <c r="Q23" s="186"/>
+      <c r="R23" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="158" t="s">
+      <c r="S23" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="T23" s="159"/>
-      <c r="U23" s="159"/>
-      <c r="V23" s="159"/>
-      <c r="W23" s="160"/>
-      <c r="X23" s="130" t="s">
+      <c r="T23" s="185"/>
+      <c r="U23" s="185"/>
+      <c r="V23" s="185"/>
+      <c r="W23" s="186"/>
+      <c r="X23" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="Y23" s="130" t="s">
+      <c r="Y23" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="Z23" s="158" t="s">
+      <c r="Z23" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="AA23" s="159"/>
-      <c r="AB23" s="159"/>
-      <c r="AC23" s="160"/>
-      <c r="AD23" s="158" t="s">
+      <c r="AA23" s="185"/>
+      <c r="AB23" s="185"/>
+      <c r="AC23" s="186"/>
+      <c r="AD23" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="AE23" s="160"/>
-    </row>
-    <row r="24" spans="1:31" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="169">
-        <v>1</v>
-      </c>
-      <c r="B24" s="169"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="170"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="170"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="170"/>
-      <c r="J24" s="170"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="170"/>
-      <c r="O24" s="169"/>
-      <c r="P24" s="169"/>
-      <c r="Q24" s="169"/>
-      <c r="R24" s="132" t="s">
-        <v>45</v>
-      </c>
-      <c r="S24" s="170"/>
-      <c r="T24" s="170"/>
-      <c r="U24" s="170"/>
-      <c r="V24" s="170"/>
-      <c r="W24" s="170"/>
-      <c r="X24" s="131"/>
-      <c r="Y24" s="131"/>
-      <c r="Z24" s="170"/>
-      <c r="AA24" s="170"/>
-      <c r="AB24" s="170"/>
-      <c r="AC24" s="170"/>
-      <c r="AD24" s="169"/>
-      <c r="AE24" s="169"/>
-    </row>
-    <row r="25" spans="1:31" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="169">
-        <v>2</v>
-      </c>
-      <c r="B25" s="169"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="170"/>
-      <c r="E25" s="170"/>
-      <c r="F25" s="170"/>
-      <c r="G25" s="170"/>
-      <c r="H25" s="170"/>
-      <c r="I25" s="170"/>
-      <c r="J25" s="170"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="170"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="170"/>
-      <c r="O25" s="169"/>
-      <c r="P25" s="169"/>
-      <c r="Q25" s="169"/>
-      <c r="R25" s="132" t="s">
-        <v>45</v>
-      </c>
-      <c r="S25" s="170"/>
-      <c r="T25" s="170"/>
-      <c r="U25" s="170"/>
-      <c r="V25" s="170"/>
-      <c r="W25" s="170"/>
-      <c r="X25" s="131"/>
-      <c r="Y25" s="131"/>
-      <c r="Z25" s="170"/>
-      <c r="AA25" s="170"/>
-      <c r="AB25" s="170"/>
-      <c r="AC25" s="170"/>
-      <c r="AD25" s="169"/>
-      <c r="AE25" s="169"/>
-    </row>
-    <row r="26" spans="1:31" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="169">
-        <v>3</v>
-      </c>
-      <c r="B26" s="169"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="170"/>
-      <c r="F26" s="170"/>
-      <c r="G26" s="170"/>
-      <c r="H26" s="170"/>
-      <c r="I26" s="170"/>
-      <c r="J26" s="170"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="170"/>
-      <c r="M26" s="170"/>
-      <c r="N26" s="170"/>
-      <c r="O26" s="169"/>
-      <c r="P26" s="169"/>
-      <c r="Q26" s="169"/>
-      <c r="R26" s="132" t="s">
-        <v>45</v>
-      </c>
-      <c r="S26" s="170"/>
-      <c r="T26" s="170"/>
-      <c r="U26" s="170"/>
-      <c r="V26" s="170"/>
-      <c r="W26" s="170"/>
-      <c r="X26" s="131"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="170"/>
-      <c r="AA26" s="170"/>
-      <c r="AB26" s="170"/>
-      <c r="AC26" s="170"/>
-      <c r="AD26" s="169"/>
-      <c r="AE26" s="169"/>
-    </row>
-    <row r="27" spans="1:31" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="169">
-        <v>4</v>
-      </c>
-      <c r="B27" s="169"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="170"/>
-      <c r="E27" s="170"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="169"/>
-      <c r="P27" s="169"/>
-      <c r="Q27" s="169"/>
-      <c r="R27" s="132" t="s">
-        <v>45</v>
-      </c>
-      <c r="S27" s="170"/>
-      <c r="T27" s="170"/>
-      <c r="U27" s="170"/>
-      <c r="V27" s="170"/>
-      <c r="W27" s="170"/>
-      <c r="X27" s="131"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="170"/>
-      <c r="AA27" s="170"/>
-      <c r="AB27" s="170"/>
-      <c r="AC27" s="170"/>
-      <c r="AD27" s="169"/>
-      <c r="AE27" s="169"/>
-    </row>
-    <row r="28" spans="1:31" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="169">
-        <v>5</v>
-      </c>
-      <c r="B28" s="169"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="169"/>
-      <c r="P28" s="169"/>
-      <c r="Q28" s="169"/>
-      <c r="R28" s="132" t="s">
-        <v>45</v>
-      </c>
-      <c r="S28" s="170"/>
-      <c r="T28" s="170"/>
-      <c r="U28" s="170"/>
-      <c r="V28" s="170"/>
-      <c r="W28" s="170"/>
-      <c r="X28" s="131"/>
-      <c r="Y28" s="131"/>
-      <c r="Z28" s="170"/>
-      <c r="AA28" s="170"/>
-      <c r="AB28" s="170"/>
-      <c r="AC28" s="170"/>
-      <c r="AD28" s="169"/>
-      <c r="AE28" s="169"/>
+      <c r="AE23" s="186"/>
+    </row>
+    <row r="24" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="142"/>
+      <c r="B24" s="142"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="142"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="142"/>
+      <c r="N24" s="142"/>
+      <c r="O24" s="142"/>
+      <c r="P24" s="142"/>
+      <c r="Q24" s="142"/>
+      <c r="S24" s="142"/>
+      <c r="T24" s="142"/>
+      <c r="U24" s="142"/>
+      <c r="V24" s="142"/>
+      <c r="W24" s="142"/>
+      <c r="Z24" s="142"/>
+      <c r="AA24" s="142"/>
+      <c r="AB24" s="142"/>
+      <c r="AC24" s="142"/>
+      <c r="AD24" s="142"/>
+      <c r="AE24" s="142"/>
+    </row>
+    <row r="25" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="141"/>
+      <c r="B25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="141"/>
+      <c r="V25" s="141"/>
+      <c r="W25" s="141"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="141"/>
+      <c r="AB25" s="141"/>
+      <c r="AC25" s="141"/>
+      <c r="AD25" s="141"/>
+      <c r="AE25" s="141"/>
+    </row>
+    <row r="26" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="141"/>
+      <c r="B26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="141"/>
+      <c r="I26" s="141"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="141"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="141"/>
+      <c r="P26" s="141"/>
+      <c r="Q26" s="141"/>
+      <c r="S26" s="141"/>
+      <c r="T26" s="141"/>
+      <c r="U26" s="141"/>
+      <c r="V26" s="141"/>
+      <c r="W26" s="141"/>
+      <c r="Z26" s="141"/>
+      <c r="AA26" s="141"/>
+      <c r="AB26" s="141"/>
+      <c r="AC26" s="141"/>
+      <c r="AD26" s="141"/>
+      <c r="AE26" s="141"/>
+    </row>
+    <row r="27" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="141"/>
+      <c r="B27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="141"/>
+      <c r="I27" s="141"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="141"/>
+      <c r="L27" s="141"/>
+      <c r="M27" s="141"/>
+      <c r="N27" s="141"/>
+      <c r="O27" s="141"/>
+      <c r="P27" s="141"/>
+      <c r="Q27" s="141"/>
+      <c r="S27" s="141"/>
+      <c r="T27" s="141"/>
+      <c r="U27" s="141"/>
+      <c r="V27" s="141"/>
+      <c r="W27" s="141"/>
+      <c r="Z27" s="141"/>
+      <c r="AA27" s="141"/>
+      <c r="AB27" s="141"/>
+      <c r="AC27" s="141"/>
+      <c r="AD27" s="141"/>
+      <c r="AE27" s="141"/>
+    </row>
+    <row r="28" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="141"/>
+      <c r="B28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="141"/>
+      <c r="Q28" s="141"/>
+      <c r="S28" s="141"/>
+      <c r="T28" s="141"/>
+      <c r="U28" s="141"/>
+      <c r="V28" s="141"/>
+      <c r="W28" s="141"/>
+      <c r="Z28" s="141"/>
+      <c r="AA28" s="141"/>
+      <c r="AB28" s="141"/>
+      <c r="AC28" s="141"/>
+      <c r="AD28" s="141"/>
+      <c r="AE28" s="141"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="141"/>
+      <c r="B29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="141"/>
+      <c r="P29" s="141"/>
+      <c r="Q29" s="141"/>
+      <c r="S29" s="141"/>
+      <c r="T29" s="141"/>
+      <c r="U29" s="141"/>
+      <c r="V29" s="141"/>
+      <c r="W29" s="141"/>
+      <c r="Z29" s="141"/>
+      <c r="AA29" s="141"/>
+      <c r="AB29" s="141"/>
+      <c r="AC29" s="141"/>
+      <c r="AD29" s="141"/>
+      <c r="AE29" s="141"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="141"/>
+      <c r="B30" s="141"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="141"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="141"/>
+      <c r="L30" s="141"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="141"/>
+      <c r="O30" s="141"/>
+      <c r="P30" s="141"/>
+      <c r="Q30" s="141"/>
+      <c r="S30" s="141"/>
+      <c r="T30" s="141"/>
+      <c r="U30" s="141"/>
+      <c r="V30" s="141"/>
+      <c r="W30" s="141"/>
+      <c r="Z30" s="141"/>
+      <c r="AA30" s="141"/>
+      <c r="AB30" s="141"/>
+      <c r="AC30" s="141"/>
+      <c r="AD30" s="141"/>
+      <c r="AE30" s="141"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="141"/>
+      <c r="B31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="141"/>
+      <c r="P31" s="141"/>
+      <c r="Q31" s="141"/>
+      <c r="S31" s="141"/>
+      <c r="T31" s="141"/>
+      <c r="U31" s="141"/>
+      <c r="V31" s="141"/>
+      <c r="W31" s="141"/>
+      <c r="Z31" s="141"/>
+      <c r="AA31" s="141"/>
+      <c r="AB31" s="141"/>
+      <c r="AC31" s="141"/>
+      <c r="AD31" s="141"/>
+      <c r="AE31" s="141"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="141"/>
+      <c r="B32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
+      <c r="H32" s="141"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="141"/>
+      <c r="K32" s="141"/>
+      <c r="L32" s="141"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="141"/>
+      <c r="O32" s="141"/>
+      <c r="P32" s="141"/>
+      <c r="Q32" s="141"/>
+      <c r="S32" s="141"/>
+      <c r="T32" s="141"/>
+      <c r="U32" s="141"/>
+      <c r="V32" s="141"/>
+      <c r="W32" s="141"/>
+      <c r="Z32" s="141"/>
+      <c r="AA32" s="141"/>
+      <c r="AB32" s="141"/>
+      <c r="AC32" s="141"/>
+      <c r="AD32" s="141"/>
+      <c r="AE32" s="141"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="141"/>
+      <c r="B33" s="141"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="141"/>
+      <c r="H33" s="141"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="141"/>
+      <c r="K33" s="141"/>
+      <c r="L33" s="141"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="141"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="141"/>
+      <c r="S33" s="141"/>
+      <c r="T33" s="141"/>
+      <c r="U33" s="141"/>
+      <c r="V33" s="141"/>
+      <c r="W33" s="141"/>
+      <c r="Z33" s="141"/>
+      <c r="AA33" s="141"/>
+      <c r="AB33" s="141"/>
+      <c r="AC33" s="141"/>
+      <c r="AD33" s="141"/>
+      <c r="AE33" s="141"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A34" s="141"/>
+      <c r="B34" s="141"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="141"/>
+      <c r="H34" s="141"/>
+      <c r="I34" s="141"/>
+      <c r="J34" s="141"/>
+      <c r="K34" s="141"/>
+      <c r="L34" s="141"/>
+      <c r="M34" s="141"/>
+      <c r="N34" s="141"/>
+      <c r="O34" s="141"/>
+      <c r="P34" s="141"/>
+      <c r="Q34" s="141"/>
+      <c r="S34" s="141"/>
+      <c r="T34" s="141"/>
+      <c r="U34" s="141"/>
+      <c r="V34" s="141"/>
+      <c r="W34" s="141"/>
+      <c r="Z34" s="141"/>
+      <c r="AA34" s="141"/>
+      <c r="AB34" s="141"/>
+      <c r="AC34" s="141"/>
+      <c r="AD34" s="141"/>
+      <c r="AE34" s="141"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A35" s="141"/>
+      <c r="B35" s="141"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="141"/>
+      <c r="H35" s="141"/>
+      <c r="I35" s="141"/>
+      <c r="J35" s="141"/>
+      <c r="K35" s="141"/>
+      <c r="L35" s="141"/>
+      <c r="M35" s="141"/>
+      <c r="N35" s="141"/>
+      <c r="O35" s="141"/>
+      <c r="P35" s="141"/>
+      <c r="Q35" s="141"/>
+      <c r="S35" s="141"/>
+      <c r="T35" s="141"/>
+      <c r="U35" s="141"/>
+      <c r="V35" s="141"/>
+      <c r="W35" s="141"/>
+      <c r="Z35" s="141"/>
+      <c r="AA35" s="141"/>
+      <c r="AB35" s="141"/>
+      <c r="AC35" s="141"/>
+      <c r="AD35" s="141"/>
+      <c r="AE35" s="141"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A36" s="141"/>
+      <c r="B36" s="141"/>
+      <c r="D36" s="141"/>
+      <c r="E36" s="141"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="141"/>
+      <c r="H36" s="141"/>
+      <c r="I36" s="141"/>
+      <c r="J36" s="141"/>
+      <c r="K36" s="141"/>
+      <c r="L36" s="141"/>
+      <c r="M36" s="141"/>
+      <c r="N36" s="141"/>
+      <c r="O36" s="141"/>
+      <c r="P36" s="141"/>
+      <c r="Q36" s="141"/>
+      <c r="S36" s="141"/>
+      <c r="T36" s="141"/>
+      <c r="U36" s="141"/>
+      <c r="V36" s="141"/>
+      <c r="W36" s="141"/>
+      <c r="Z36" s="141"/>
+      <c r="AA36" s="141"/>
+      <c r="AB36" s="141"/>
+      <c r="AC36" s="141"/>
+      <c r="AD36" s="141"/>
+      <c r="AE36" s="141"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A37" s="141"/>
+      <c r="B37" s="141"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="141"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
+      <c r="H37" s="141"/>
+      <c r="I37" s="141"/>
+      <c r="J37" s="141"/>
+      <c r="K37" s="141"/>
+      <c r="L37" s="141"/>
+      <c r="M37" s="141"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="141"/>
+      <c r="P37" s="141"/>
+      <c r="Q37" s="141"/>
+      <c r="S37" s="141"/>
+      <c r="T37" s="141"/>
+      <c r="U37" s="141"/>
+      <c r="V37" s="141"/>
+      <c r="W37" s="141"/>
+      <c r="Z37" s="141"/>
+      <c r="AA37" s="141"/>
+      <c r="AB37" s="141"/>
+      <c r="AC37" s="141"/>
+      <c r="AD37" s="141"/>
+      <c r="AE37" s="141"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A38" s="141"/>
+      <c r="B38" s="141"/>
+      <c r="D38" s="141"/>
+      <c r="E38" s="141"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="141"/>
+      <c r="H38" s="141"/>
+      <c r="I38" s="141"/>
+      <c r="J38" s="141"/>
+      <c r="K38" s="141"/>
+      <c r="L38" s="141"/>
+      <c r="M38" s="141"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="141"/>
+      <c r="P38" s="141"/>
+      <c r="Q38" s="141"/>
+      <c r="S38" s="141"/>
+      <c r="T38" s="141"/>
+      <c r="U38" s="141"/>
+      <c r="V38" s="141"/>
+      <c r="W38" s="141"/>
+      <c r="Z38" s="141"/>
+      <c r="AA38" s="141"/>
+      <c r="AB38" s="141"/>
+      <c r="AC38" s="141"/>
+      <c r="AD38" s="141"/>
+      <c r="AE38" s="141"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A39" s="141"/>
+      <c r="B39" s="141"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="141"/>
+      <c r="I39" s="141"/>
+      <c r="J39" s="141"/>
+      <c r="K39" s="141"/>
+      <c r="L39" s="141"/>
+      <c r="M39" s="141"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="141"/>
+      <c r="P39" s="141"/>
+      <c r="Q39" s="141"/>
+      <c r="S39" s="141"/>
+      <c r="T39" s="141"/>
+      <c r="U39" s="141"/>
+      <c r="V39" s="141"/>
+      <c r="W39" s="141"/>
+      <c r="Z39" s="141"/>
+      <c r="AA39" s="141"/>
+      <c r="AB39" s="141"/>
+      <c r="AC39" s="141"/>
+      <c r="AD39" s="141"/>
+      <c r="AE39" s="141"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A40" s="141"/>
+      <c r="B40" s="141"/>
+      <c r="D40" s="141"/>
+      <c r="E40" s="141"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="141"/>
+      <c r="I40" s="141"/>
+      <c r="J40" s="141"/>
+      <c r="K40" s="141"/>
+      <c r="L40" s="141"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="141"/>
+      <c r="P40" s="141"/>
+      <c r="Q40" s="141"/>
+      <c r="S40" s="141"/>
+      <c r="T40" s="141"/>
+      <c r="U40" s="141"/>
+      <c r="V40" s="141"/>
+      <c r="W40" s="141"/>
+      <c r="Z40" s="141"/>
+      <c r="AA40" s="141"/>
+      <c r="AB40" s="141"/>
+      <c r="AC40" s="141"/>
+      <c r="AD40" s="141"/>
+      <c r="AE40" s="141"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A41" s="141"/>
+      <c r="B41" s="141"/>
+      <c r="D41" s="141"/>
+      <c r="E41" s="141"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="141"/>
+      <c r="I41" s="141"/>
+      <c r="J41" s="141"/>
+      <c r="K41" s="141"/>
+      <c r="L41" s="141"/>
+      <c r="M41" s="141"/>
+      <c r="N41" s="141"/>
+      <c r="O41" s="141"/>
+      <c r="P41" s="141"/>
+      <c r="Q41" s="141"/>
+      <c r="S41" s="141"/>
+      <c r="T41" s="141"/>
+      <c r="U41" s="141"/>
+      <c r="V41" s="141"/>
+      <c r="W41" s="141"/>
+      <c r="Z41" s="141"/>
+      <c r="AA41" s="141"/>
+      <c r="AB41" s="141"/>
+      <c r="AC41" s="141"/>
+      <c r="AD41" s="141"/>
+      <c r="AE41" s="141"/>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A42" s="141"/>
+      <c r="B42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="141"/>
+      <c r="I42" s="141"/>
+      <c r="J42" s="141"/>
+      <c r="K42" s="141"/>
+      <c r="L42" s="141"/>
+      <c r="M42" s="141"/>
+      <c r="N42" s="141"/>
+      <c r="O42" s="141"/>
+      <c r="P42" s="141"/>
+      <c r="Q42" s="141"/>
+      <c r="S42" s="141"/>
+      <c r="T42" s="141"/>
+      <c r="U42" s="141"/>
+      <c r="V42" s="141"/>
+      <c r="W42" s="141"/>
+      <c r="Z42" s="141"/>
+      <c r="AA42" s="141"/>
+      <c r="AB42" s="141"/>
+      <c r="AC42" s="141"/>
+      <c r="AD42" s="141"/>
+      <c r="AE42" s="141"/>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A43" s="141"/>
+      <c r="B43" s="141"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="141"/>
+      <c r="I43" s="141"/>
+      <c r="J43" s="141"/>
+      <c r="K43" s="141"/>
+      <c r="L43" s="141"/>
+      <c r="M43" s="141"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="141"/>
+      <c r="P43" s="141"/>
+      <c r="Q43" s="141"/>
+      <c r="S43" s="141"/>
+      <c r="T43" s="141"/>
+      <c r="U43" s="141"/>
+      <c r="V43" s="141"/>
+      <c r="W43" s="141"/>
+      <c r="Z43" s="141"/>
+      <c r="AA43" s="141"/>
+      <c r="AB43" s="141"/>
+      <c r="AC43" s="141"/>
+      <c r="AD43" s="141"/>
+      <c r="AE43" s="141"/>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A44" s="141"/>
+      <c r="B44" s="141"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="141"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="141"/>
+      <c r="H44" s="141"/>
+      <c r="I44" s="141"/>
+      <c r="J44" s="141"/>
+      <c r="K44" s="141"/>
+      <c r="L44" s="141"/>
+      <c r="M44" s="141"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="141"/>
+      <c r="P44" s="141"/>
+      <c r="Q44" s="141"/>
+      <c r="S44" s="141"/>
+      <c r="T44" s="141"/>
+      <c r="U44" s="141"/>
+      <c r="V44" s="141"/>
+      <c r="W44" s="141"/>
+      <c r="Z44" s="141"/>
+      <c r="AA44" s="141"/>
+      <c r="AB44" s="141"/>
+      <c r="AC44" s="141"/>
+      <c r="AD44" s="141"/>
+      <c r="AE44" s="141"/>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A45" s="141"/>
+      <c r="B45" s="141"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="141"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="141"/>
+      <c r="I45" s="141"/>
+      <c r="J45" s="141"/>
+      <c r="K45" s="141"/>
+      <c r="L45" s="141"/>
+      <c r="M45" s="141"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="141"/>
+      <c r="P45" s="141"/>
+      <c r="Q45" s="141"/>
+      <c r="S45" s="141"/>
+      <c r="T45" s="141"/>
+      <c r="U45" s="141"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="141"/>
+      <c r="Z45" s="141"/>
+      <c r="AA45" s="141"/>
+      <c r="AB45" s="141"/>
+      <c r="AC45" s="141"/>
+      <c r="AD45" s="141"/>
+      <c r="AE45" s="141"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A46" s="141"/>
+      <c r="B46" s="141"/>
+      <c r="D46" s="141"/>
+      <c r="E46" s="141"/>
+      <c r="F46" s="141"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="141"/>
+      <c r="I46" s="141"/>
+      <c r="J46" s="141"/>
+      <c r="K46" s="141"/>
+      <c r="L46" s="141"/>
+      <c r="M46" s="141"/>
+      <c r="N46" s="141"/>
+      <c r="O46" s="141"/>
+      <c r="P46" s="141"/>
+      <c r="Q46" s="141"/>
+      <c r="S46" s="141"/>
+      <c r="T46" s="141"/>
+      <c r="U46" s="141"/>
+      <c r="V46" s="141"/>
+      <c r="W46" s="141"/>
+      <c r="Z46" s="141"/>
+      <c r="AA46" s="141"/>
+      <c r="AB46" s="141"/>
+      <c r="AC46" s="141"/>
+      <c r="AD46" s="141"/>
+      <c r="AE46" s="141"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A47" s="141"/>
+      <c r="B47" s="141"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="141"/>
+      <c r="I47" s="141"/>
+      <c r="J47" s="141"/>
+      <c r="K47" s="141"/>
+      <c r="L47" s="141"/>
+      <c r="M47" s="141"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="141"/>
+      <c r="P47" s="141"/>
+      <c r="Q47" s="141"/>
+      <c r="S47" s="141"/>
+      <c r="T47" s="141"/>
+      <c r="U47" s="141"/>
+      <c r="V47" s="141"/>
+      <c r="W47" s="141"/>
+      <c r="Z47" s="141"/>
+      <c r="AA47" s="141"/>
+      <c r="AB47" s="141"/>
+      <c r="AC47" s="141"/>
+      <c r="AD47" s="141"/>
+      <c r="AE47" s="141"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A48" s="141"/>
+      <c r="B48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
+      <c r="F48" s="141"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="141"/>
+      <c r="I48" s="141"/>
+      <c r="J48" s="141"/>
+      <c r="K48" s="141"/>
+      <c r="L48" s="141"/>
+      <c r="M48" s="141"/>
+      <c r="N48" s="141"/>
+      <c r="O48" s="141"/>
+      <c r="P48" s="141"/>
+      <c r="Q48" s="141"/>
+      <c r="S48" s="141"/>
+      <c r="T48" s="141"/>
+      <c r="U48" s="141"/>
+      <c r="V48" s="141"/>
+      <c r="W48" s="141"/>
+      <c r="Z48" s="141"/>
+      <c r="AA48" s="141"/>
+      <c r="AB48" s="141"/>
+      <c r="AC48" s="141"/>
+      <c r="AD48" s="141"/>
+      <c r="AE48" s="141"/>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A49" s="141"/>
+      <c r="B49" s="141"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="141"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="141"/>
+      <c r="I49" s="141"/>
+      <c r="J49" s="141"/>
+      <c r="K49" s="141"/>
+      <c r="L49" s="141"/>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141"/>
+      <c r="O49" s="141"/>
+      <c r="P49" s="141"/>
+      <c r="Q49" s="141"/>
+      <c r="S49" s="141"/>
+      <c r="T49" s="141"/>
+      <c r="U49" s="141"/>
+      <c r="V49" s="141"/>
+      <c r="W49" s="141"/>
+      <c r="Z49" s="141"/>
+      <c r="AA49" s="141"/>
+      <c r="AB49" s="141"/>
+      <c r="AC49" s="141"/>
+      <c r="AD49" s="141"/>
+      <c r="AE49" s="141"/>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A50" s="141"/>
+      <c r="B50" s="141"/>
+      <c r="D50" s="141"/>
+      <c r="E50" s="141"/>
+      <c r="F50" s="141"/>
+      <c r="G50" s="141"/>
+      <c r="H50" s="141"/>
+      <c r="I50" s="141"/>
+      <c r="J50" s="141"/>
+      <c r="K50" s="141"/>
+      <c r="L50" s="141"/>
+      <c r="M50" s="141"/>
+      <c r="N50" s="141"/>
+      <c r="O50" s="141"/>
+      <c r="P50" s="141"/>
+      <c r="Q50" s="141"/>
+      <c r="S50" s="141"/>
+      <c r="T50" s="141"/>
+      <c r="U50" s="141"/>
+      <c r="V50" s="141"/>
+      <c r="W50" s="141"/>
+      <c r="Z50" s="141"/>
+      <c r="AA50" s="141"/>
+      <c r="AB50" s="141"/>
+      <c r="AC50" s="141"/>
+      <c r="AD50" s="141"/>
+      <c r="AE50" s="141"/>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A51" s="141"/>
+      <c r="B51" s="141"/>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A52" s="141"/>
+      <c r="B52" s="141"/>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A53" s="141"/>
+      <c r="B53" s="141"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A54" s="141"/>
+      <c r="B54" s="141"/>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A55" s="141"/>
+      <c r="B55" s="141"/>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A56" s="141"/>
+      <c r="B56" s="141"/>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A57" s="141"/>
+      <c r="B57" s="141"/>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A58" s="141"/>
+      <c r="B58" s="141"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A59" s="141"/>
+      <c r="B59" s="141"/>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A60" s="141"/>
+      <c r="B60" s="141"/>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A61" s="141"/>
+      <c r="B61" s="141"/>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A62" s="141"/>
+      <c r="B62" s="141"/>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A63" s="141"/>
+      <c r="B63" s="141"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A64" s="141"/>
+      <c r="B64" s="141"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="141"/>
+      <c r="B65" s="141"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="141"/>
+      <c r="B66" s="141"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="141"/>
+      <c r="B67" s="141"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="141"/>
+      <c r="B68" s="141"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="141"/>
+      <c r="B69" s="141"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="141"/>
+      <c r="B70" s="141"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="141"/>
+      <c r="B71" s="141"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="141"/>
+      <c r="B72" s="141"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="141"/>
+      <c r="B73" s="141"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="141"/>
+      <c r="B74" s="141"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="141"/>
+      <c r="B75" s="141"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="141"/>
+      <c r="B76" s="141"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="141"/>
+      <c r="B77" s="141"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="141"/>
+      <c r="B78" s="141"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="141"/>
+      <c r="B79" s="141"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="141"/>
+      <c r="B80" s="141"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="141"/>
+      <c r="B81" s="141"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="141"/>
+      <c r="B82" s="141"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="141"/>
+      <c r="B83" s="141"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="141"/>
+      <c r="B84" s="141"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="141"/>
+      <c r="B85" s="141"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="141"/>
+      <c r="B86" s="141"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="141"/>
+      <c r="B87" s="141"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="141"/>
+      <c r="B88" s="141"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="141"/>
+      <c r="B89" s="141"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="141"/>
+      <c r="B90" s="141"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="141"/>
+      <c r="B91" s="141"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="141"/>
+      <c r="B92" s="141"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="141"/>
+      <c r="B93" s="141"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="141"/>
+      <c r="B94" s="141"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="141"/>
+      <c r="B95" s="141"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="141"/>
+      <c r="B96" s="141"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="141"/>
+      <c r="B97" s="141"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="141"/>
+      <c r="B98" s="141"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="141"/>
+      <c r="B99" s="141"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="141"/>
+      <c r="B100" s="141"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="141"/>
+      <c r="B101" s="141"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="141"/>
+      <c r="B102" s="141"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="141"/>
+      <c r="B103" s="141"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="141"/>
+      <c r="B104" s="141"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="141"/>
+      <c r="B105" s="141"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="141"/>
+      <c r="B106" s="141"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="141"/>
+      <c r="B107" s="141"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="141"/>
+      <c r="B108" s="141"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="141"/>
+      <c r="B109" s="141"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="141"/>
+      <c r="B110" s="141"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="141"/>
+      <c r="B111" s="141"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="141"/>
+      <c r="B112" s="141"/>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="141"/>
+      <c r="B113" s="141"/>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="141"/>
+      <c r="B114" s="141"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="141"/>
+      <c r="B115" s="141"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="141"/>
+      <c r="B116" s="141"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="141"/>
+      <c r="B117" s="141"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="141"/>
+      <c r="B118" s="141"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="141"/>
+      <c r="B119" s="141"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="141"/>
+      <c r="B120" s="141"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="141"/>
+      <c r="B121" s="141"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="141"/>
+      <c r="B122" s="141"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="141"/>
+      <c r="B123" s="141"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="141"/>
+      <c r="B124" s="141"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="141"/>
+      <c r="B125" s="141"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="141"/>
+      <c r="B126" s="141"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="141"/>
+      <c r="B127" s="141"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="141"/>
+      <c r="B128" s="141"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="141"/>
+      <c r="B129" s="141"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="141"/>
+      <c r="B130" s="141"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="141"/>
+      <c r="B131" s="141"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="141"/>
+      <c r="B132" s="141"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="141"/>
+      <c r="B133" s="141"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="141"/>
+      <c r="B134" s="141"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="141"/>
+      <c r="B135" s="141"/>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="141"/>
+      <c r="B136" s="141"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="141"/>
+      <c r="B137" s="141"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="141"/>
+      <c r="B138" s="141"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="141"/>
+      <c r="B139" s="141"/>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="141"/>
+      <c r="B140" s="141"/>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="141"/>
+      <c r="B141" s="141"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="141"/>
+      <c r="B142" s="141"/>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="141"/>
+      <c r="B143" s="141"/>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="141"/>
+      <c r="B144" s="141"/>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="141"/>
+      <c r="B145" s="141"/>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="141"/>
+      <c r="B146" s="141"/>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="141"/>
+      <c r="B147" s="141"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="141"/>
+      <c r="B148" s="141"/>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="141"/>
+      <c r="B149" s="141"/>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="141"/>
+      <c r="B150" s="141"/>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="141"/>
+      <c r="B151" s="141"/>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="141"/>
+      <c r="B152" s="141"/>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="141"/>
+      <c r="B153" s="141"/>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="141"/>
+      <c r="B154" s="141"/>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="141"/>
+      <c r="B155" s="141"/>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="141"/>
+      <c r="B156" s="141"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="141"/>
+      <c r="B157" s="141"/>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="141"/>
+      <c r="B158" s="141"/>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="141"/>
+      <c r="B159" s="141"/>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="141"/>
+      <c r="B160" s="141"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="141"/>
+      <c r="B161" s="141"/>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="141"/>
+      <c r="B162" s="141"/>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="141"/>
+      <c r="B163" s="141"/>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="141"/>
+      <c r="B164" s="141"/>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="141"/>
+      <c r="B165" s="141"/>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="141"/>
+      <c r="B166" s="141"/>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="141"/>
+      <c r="B167" s="141"/>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="141"/>
+      <c r="B168" s="141"/>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="141"/>
+      <c r="B169" s="141"/>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="141"/>
+      <c r="B170" s="141"/>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="141"/>
+      <c r="B171" s="141"/>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="141"/>
+      <c r="B172" s="141"/>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="141"/>
+      <c r="B173" s="141"/>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="141"/>
+      <c r="B174" s="141"/>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="141"/>
+      <c r="B175" s="141"/>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="141"/>
+      <c r="B176" s="141"/>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="141"/>
+      <c r="B177" s="141"/>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="141"/>
+      <c r="B178" s="141"/>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="141"/>
+      <c r="B179" s="141"/>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="141"/>
+      <c r="B180" s="141"/>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="141"/>
+      <c r="B181" s="141"/>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="141"/>
+      <c r="B182" s="141"/>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="141"/>
+      <c r="B183" s="141"/>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="141"/>
+      <c r="B184" s="141"/>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="141"/>
+      <c r="B185" s="141"/>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="141"/>
+      <c r="B186" s="141"/>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="141"/>
+      <c r="B187" s="141"/>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="141"/>
+      <c r="B188" s="141"/>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="141"/>
+      <c r="B189" s="141"/>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="141"/>
+      <c r="B190" s="141"/>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="141"/>
+      <c r="B191" s="141"/>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="141"/>
+      <c r="B192" s="141"/>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="141"/>
+      <c r="B193" s="141"/>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="141"/>
+      <c r="B194" s="141"/>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="141"/>
+      <c r="B195" s="141"/>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="141"/>
+      <c r="B196" s="141"/>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="141"/>
+      <c r="B197" s="141"/>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="141"/>
+      <c r="B198" s="141"/>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="141"/>
+      <c r="B199" s="141"/>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="141"/>
+      <c r="B200" s="141"/>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="141"/>
+      <c r="B201" s="141"/>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="141"/>
+      <c r="B202" s="141"/>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="141"/>
+      <c r="B203" s="141"/>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="141"/>
+      <c r="B204" s="141"/>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="141"/>
+      <c r="B205" s="141"/>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="141"/>
+      <c r="B206" s="141"/>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="141"/>
+      <c r="B207" s="141"/>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="141"/>
+      <c r="B208" s="141"/>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="141"/>
+      <c r="B209" s="141"/>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="141"/>
+      <c r="B210" s="141"/>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="141"/>
+      <c r="B211" s="141"/>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="141"/>
+      <c r="B212" s="141"/>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="141"/>
+      <c r="B213" s="141"/>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="141"/>
+      <c r="B214" s="141"/>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="141"/>
+      <c r="B215" s="141"/>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="141"/>
+      <c r="B216" s="141"/>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="141"/>
+      <c r="B217" s="141"/>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="141"/>
+      <c r="B218" s="141"/>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="141"/>
+      <c r="B219" s="141"/>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="141"/>
+      <c r="B220" s="141"/>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="141"/>
+      <c r="B221" s="141"/>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="141"/>
+      <c r="B222" s="141"/>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="141"/>
+      <c r="B223" s="141"/>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="141"/>
+      <c r="B224" s="141"/>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="141"/>
+      <c r="B225" s="141"/>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="141"/>
+      <c r="B226" s="141"/>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="141"/>
+      <c r="B227" s="141"/>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="141"/>
+      <c r="B228" s="141"/>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="141"/>
+      <c r="B229" s="141"/>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="141"/>
+      <c r="B230" s="141"/>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="141"/>
+      <c r="B231" s="141"/>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="141"/>
+      <c r="B232" s="141"/>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="141"/>
+      <c r="B233" s="141"/>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="141"/>
+      <c r="B234" s="141"/>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="141"/>
+      <c r="B235" s="141"/>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="141"/>
+      <c r="B236" s="141"/>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="141"/>
+      <c r="B237" s="141"/>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="141"/>
+      <c r="B238" s="141"/>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="141"/>
+      <c r="B239" s="141"/>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="141"/>
+      <c r="B240" s="141"/>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="141"/>
+      <c r="B241" s="141"/>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="141"/>
+      <c r="B242" s="141"/>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="141"/>
+      <c r="B243" s="141"/>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="141"/>
+      <c r="B244" s="141"/>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="141"/>
+      <c r="B245" s="141"/>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="141"/>
+      <c r="B246" s="141"/>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="141"/>
+      <c r="B247" s="141"/>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="141"/>
+      <c r="B248" s="141"/>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="141"/>
+      <c r="B249" s="141"/>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="141"/>
+      <c r="B250" s="141"/>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="141"/>
+      <c r="B251" s="141"/>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="141"/>
+      <c r="B252" s="141"/>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="141"/>
+      <c r="B253" s="141"/>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="141"/>
+      <c r="B254" s="141"/>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="141"/>
+      <c r="B255" s="141"/>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="141"/>
+      <c r="B256" s="141"/>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="141"/>
+      <c r="B257" s="141"/>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="141"/>
+      <c r="B258" s="141"/>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="141"/>
+      <c r="B259" s="141"/>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="141"/>
+      <c r="B260" s="141"/>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="141"/>
+      <c r="B261" s="141"/>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="141"/>
+      <c r="B262" s="141"/>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="141"/>
+      <c r="B263" s="141"/>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="141"/>
+      <c r="B264" s="141"/>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="141"/>
+      <c r="B265" s="141"/>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="141"/>
+      <c r="B266" s="141"/>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="141"/>
+      <c r="B267" s="141"/>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="141"/>
+      <c r="B268" s="141"/>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="141"/>
+      <c r="B269" s="141"/>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="141"/>
+      <c r="B270" s="141"/>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="141"/>
+      <c r="B271" s="141"/>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="141"/>
+      <c r="B272" s="141"/>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="141"/>
+      <c r="B273" s="141"/>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="141"/>
+      <c r="B274" s="141"/>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="141"/>
+      <c r="B275" s="141"/>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="141"/>
+      <c r="B276" s="141"/>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="141"/>
+      <c r="B277" s="141"/>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="141"/>
+      <c r="B278" s="141"/>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="141"/>
+      <c r="B279" s="141"/>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="141"/>
+      <c r="B280" s="141"/>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="141"/>
+      <c r="B281" s="141"/>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="141"/>
+      <c r="B282" s="141"/>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="141"/>
+      <c r="B283" s="141"/>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="141"/>
+      <c r="B284" s="141"/>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="141"/>
+      <c r="B285" s="141"/>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="141"/>
+      <c r="B286" s="141"/>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="141"/>
+      <c r="B287" s="141"/>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="141"/>
+      <c r="B288" s="141"/>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="141"/>
+      <c r="B289" s="141"/>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="141"/>
+      <c r="B290" s="141"/>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="141"/>
+      <c r="B291" s="141"/>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="141"/>
+      <c r="B292" s="141"/>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="141"/>
+      <c r="B293" s="141"/>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="141"/>
+      <c r="B294" s="141"/>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="141"/>
+      <c r="B295" s="141"/>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="141"/>
+      <c r="B296" s="141"/>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="141"/>
+      <c r="B297" s="141"/>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="141"/>
+      <c r="B298" s="141"/>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="141"/>
+      <c r="B299" s="141"/>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="141"/>
+      <c r="B300" s="141"/>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="141"/>
+      <c r="B301" s="141"/>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="141"/>
+      <c r="B302" s="141"/>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="141"/>
+      <c r="B303" s="141"/>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="141"/>
+      <c r="B304" s="141"/>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="141"/>
+      <c r="B305" s="141"/>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="141"/>
+      <c r="B306" s="141"/>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="141"/>
+      <c r="B307" s="141"/>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="141"/>
+      <c r="B308" s="141"/>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="141"/>
+      <c r="B309" s="141"/>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="141"/>
+      <c r="B310" s="141"/>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="141"/>
+      <c r="B311" s="141"/>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="141"/>
+      <c r="B312" s="141"/>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="141"/>
+      <c r="B313" s="141"/>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="141"/>
+      <c r="B314" s="141"/>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="141"/>
+      <c r="B315" s="141"/>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="141"/>
+      <c r="B316" s="141"/>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="141"/>
+      <c r="B317" s="141"/>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="141"/>
+      <c r="B318" s="141"/>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="141"/>
+      <c r="B319" s="141"/>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="141"/>
+      <c r="B320" s="141"/>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="141"/>
+      <c r="B321" s="141"/>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="141"/>
+      <c r="B322" s="141"/>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" s="141"/>
+      <c r="B323" s="141"/>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" s="141"/>
+      <c r="B324" s="141"/>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" s="141"/>
+      <c r="B325" s="141"/>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" s="141"/>
+      <c r="B326" s="141"/>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" s="141"/>
+      <c r="B327" s="141"/>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" s="141"/>
+      <c r="B328" s="141"/>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" s="141"/>
+      <c r="B329" s="141"/>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" s="141"/>
+      <c r="B330" s="141"/>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" s="141"/>
+      <c r="B331" s="141"/>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" s="141"/>
+      <c r="B332" s="141"/>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" s="141"/>
+      <c r="B333" s="141"/>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" s="141"/>
+      <c r="B334" s="141"/>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="141"/>
+      <c r="B335" s="141"/>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="141"/>
+      <c r="B336" s="141"/>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="141"/>
+      <c r="B337" s="141"/>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="141"/>
+      <c r="B338" s="141"/>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="141"/>
+      <c r="B339" s="141"/>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="141"/>
+      <c r="B340" s="141"/>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="141"/>
+      <c r="B341" s="141"/>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="141"/>
+      <c r="B342" s="141"/>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="141"/>
+      <c r="B343" s="141"/>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="141"/>
+      <c r="B344" s="141"/>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="141"/>
+      <c r="B345" s="141"/>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="141"/>
+      <c r="B346" s="141"/>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="141"/>
+      <c r="B347" s="141"/>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="141"/>
+      <c r="B348" s="141"/>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="141"/>
+      <c r="B349" s="141"/>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="141"/>
+      <c r="B350" s="141"/>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="141"/>
+      <c r="B351" s="141"/>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="141"/>
+      <c r="B352" s="141"/>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="141"/>
+      <c r="B353" s="141"/>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="141"/>
+      <c r="B354" s="141"/>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="141"/>
+      <c r="B355" s="141"/>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="141"/>
+      <c r="B356" s="141"/>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="141"/>
+      <c r="B357" s="141"/>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="141"/>
+      <c r="B358" s="141"/>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="141"/>
+      <c r="B359" s="141"/>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="141"/>
+      <c r="B360" s="141"/>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="141"/>
+      <c r="B361" s="141"/>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="141"/>
+      <c r="B362" s="141"/>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="141"/>
+      <c r="B363" s="141"/>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="141"/>
+      <c r="B364" s="141"/>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="141"/>
+      <c r="B365" s="141"/>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="141"/>
+      <c r="B366" s="141"/>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="141"/>
+      <c r="B367" s="141"/>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="141"/>
+      <c r="B368" s="141"/>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="141"/>
+      <c r="B369" s="141"/>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="141"/>
+      <c r="B370" s="141"/>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="141"/>
+      <c r="B371" s="141"/>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="141"/>
+      <c r="B372" s="141"/>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="141"/>
+      <c r="B373" s="141"/>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="141"/>
+      <c r="B374" s="141"/>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="141"/>
+      <c r="B375" s="141"/>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="141"/>
+      <c r="B376" s="141"/>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="141"/>
+      <c r="B377" s="141"/>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="141"/>
+      <c r="B378" s="141"/>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="141"/>
+      <c r="B379" s="141"/>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="141"/>
+      <c r="B380" s="141"/>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="141"/>
+      <c r="B381" s="141"/>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="141"/>
+      <c r="B382" s="141"/>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="141"/>
+      <c r="B383" s="141"/>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="141"/>
+      <c r="B384" s="141"/>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="141"/>
+      <c r="B385" s="141"/>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="141"/>
+      <c r="B386" s="141"/>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="141"/>
+      <c r="B387" s="141"/>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="141"/>
+      <c r="B388" s="141"/>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="141"/>
+      <c r="B389" s="141"/>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="141"/>
+      <c r="B390" s="141"/>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="141"/>
+      <c r="B391" s="141"/>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="141"/>
+      <c r="B392" s="141"/>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="141"/>
+      <c r="B393" s="141"/>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="141"/>
+      <c r="B394" s="141"/>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="141"/>
+      <c r="B395" s="141"/>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="141"/>
+      <c r="B396" s="141"/>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="141"/>
+      <c r="B397" s="141"/>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="141"/>
+      <c r="B398" s="141"/>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="141"/>
+      <c r="B399" s="141"/>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="141"/>
+      <c r="B400" s="141"/>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="141"/>
+      <c r="B401" s="141"/>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="141"/>
+      <c r="B402" s="141"/>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="141"/>
+      <c r="B403" s="141"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="85">
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="J28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="S28:W28"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="S27:W27"/>
-    <mergeCell ref="Z27:AC27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="Z28:AC28"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="Z26:AC26"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="S26:W26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="J25:N25"/>
-    <mergeCell ref="J27:N27"/>
-    <mergeCell ref="S25:W25"/>
-    <mergeCell ref="Z25:AC25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="S24:W24"/>
-    <mergeCell ref="Z24:AC24"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="O25:Q25"/>
+  <mergeCells count="50">
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="Y12:AD12"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="J23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="A22:AE22"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="A5:AE5"/>
+    <mergeCell ref="A10:AE10"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="H18:AD18"/>
+    <mergeCell ref="Z23:AC23"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="F20:AE20"/>
+    <mergeCell ref="S16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="U12:X12"/>
     <mergeCell ref="Y3:AA3"/>
@@ -5152,44 +7149,6 @@
     <mergeCell ref="L7:N7"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="R3:V3"/>
-    <mergeCell ref="A22:AE22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="J24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A1:G3"/>
-    <mergeCell ref="A5:AE5"/>
-    <mergeCell ref="A10:AE10"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="H18:AD18"/>
-    <mergeCell ref="Z23:AC23"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="R2:V2"/>
-    <mergeCell ref="J23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="Y12:AD12"/>
-    <mergeCell ref="Y14:AD14"/>
-    <mergeCell ref="S23:W23"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="F20:AE20"/>
-    <mergeCell ref="S16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="B14:G14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.35433070866141736" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -5204,30 +7163,12 @@
   <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>Datos!$B$1:$C$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>C24:C28</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Datos!$B$3:$D$3</xm:f>
           </x14:formula1>
           <xm:sqref>H14:L14</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>Datos!$B$5:$G$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>R24:R28</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-          <x14:formula1>
-            <xm:f>Datos!$A$8:$CA$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>O24:Q28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C8416165-8D38-4A97-BFBD-6CA2707881AE}">
           <x14:formula1>
@@ -5250,7 +7191,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="44.5546875" customWidth="1"/>
     <col min="3" max="3" width="5.5546875" customWidth="1"/>
@@ -5258,288 +7199,288 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="223" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="224"/>
+      <c r="D1" s="223" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="D1" s="219" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" s="220"/>
+      <c r="E1" s="224"/>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -5558,7 +7499,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="34" customWidth="1"/>
     <col min="2" max="2" width="7.6640625" style="34" customWidth="1"/>
@@ -6083,76 +8024,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="224" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="226"/>
+      <c r="A1" s="228" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="230"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="221" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="223"/>
+      <c r="A2" s="225" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="226"/>
+      <c r="C2" s="226"/>
+      <c r="D2" s="227"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="C3" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>204</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="37">
         <v>3</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="66" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="37">
         <v>2</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>207</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>208</v>
       </c>
       <c r="G5" s="38"/>
     </row>
     <row r="6" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G6" s="38"/>
     </row>
@@ -6163,67 +8104,67 @@
       <c r="D7" s="52"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="221" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="222"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="223"/>
+      <c r="A8" s="225" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="227"/>
     </row>
     <row r="9" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>203</v>
-      </c>
       <c r="C9" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="35" t="s">
         <v>211</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="28">
         <v>3</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="28">
         <v>2</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="28">
         <v>1</v>
       </c>
       <c r="C12" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="29" t="s">
         <v>185</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6235,12 +8176,12 @@
       <c r="H13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="221" t="s">
-        <v>215</v>
-      </c>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="223"/>
+      <c r="A14" s="225" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="226"/>
+      <c r="C14" s="226"/>
+      <c r="D14" s="227"/>
     </row>
     <row r="15" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49"/>
@@ -6275,16 +8216,16 @@
       <c r="E19" s="41"/>
       <c r="F19" s="41"/>
       <c r="L19" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="M19" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="M19" s="43" t="s">
+      <c r="N19" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="N19" s="43" t="s">
+      <c r="O19" s="44" t="s">
         <v>189</v>
-      </c>
-      <c r="O19" s="44" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:63" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6293,16 +8234,16 @@
       <c r="C20" s="53"/>
       <c r="D20" s="54"/>
       <c r="L20" s="45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M20" s="46">
         <v>1</v>
       </c>
       <c r="N20" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="O20" s="30" t="s">
         <v>192</v>
-      </c>
-      <c r="O20" s="30" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:63" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6311,16 +8252,16 @@
       <c r="C21" s="53"/>
       <c r="D21" s="54"/>
       <c r="L21" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="M21" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="M21" s="28" t="s">
+      <c r="N21" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="O21" s="30" t="s">
         <v>195</v>
-      </c>
-      <c r="N21" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="O21" s="30" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:63" s="31" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6332,16 +8273,16 @@
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="M22" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="M22" s="28" t="s">
+      <c r="N22" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="N22" s="28" t="s">
+      <c r="O22" s="30" t="s">
         <v>199</v>
-      </c>
-      <c r="O22" s="30" t="s">
-        <v>200</v>
       </c>
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
@@ -6793,7 +8734,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="109" style="1" customWidth="1"/>
@@ -6801,17 +8742,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="227" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="227"/>
+      <c r="A1" s="231" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="231"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6819,7 +8760,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6827,7 +8768,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6835,7 +8776,7 @@
         <v>1.3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6843,7 +8784,7 @@
         <v>1.4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6851,7 +8792,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -6859,7 +8800,7 @@
         <v>2.1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6867,7 +8808,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6875,7 +8816,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6883,7 +8824,7 @@
         <v>2.4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -6891,7 +8832,7 @@
         <v>2.5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6899,7 +8840,7 @@
         <v>2.6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -6907,7 +8848,7 @@
         <v>2.7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6915,7 +8856,7 @@
         <v>2.8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -6923,7 +8864,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6931,7 +8872,7 @@
         <v>3.1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6939,7 +8880,7 @@
         <v>3.2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6947,7 +8888,7 @@
         <v>3.3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6955,7 +8896,7 @@
         <v>3.4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6963,7 +8904,7 @@
         <v>3.5</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6971,7 +8912,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6979,7 +8920,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6987,7 +8928,7 @@
         <v>4.2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6995,7 +8936,7 @@
         <v>4.3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7003,7 +8944,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7011,7 +8952,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7019,7 +8960,7 @@
         <v>4.7</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7027,7 +8968,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7035,7 +8976,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7043,7 +8984,7 @@
         <v>5.2</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7051,7 +8992,7 @@
         <v>5.3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7059,7 +9000,7 @@
         <v>5.4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7067,7 +9008,7 @@
         <v>5.5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7075,7 +9016,7 @@
         <v>5.6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7083,7 +9024,7 @@
         <v>6</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7091,7 +9032,7 @@
         <v>6.1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7099,7 +9040,7 @@
         <v>6.2</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7107,7 +9048,7 @@
         <v>6.3</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7115,7 +9056,7 @@
         <v>6.4</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7123,7 +9064,7 @@
         <v>6.5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7131,7 +9072,7 @@
         <v>6.6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7139,7 +9080,7 @@
         <v>7</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7147,7 +9088,7 @@
         <v>7.1</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7155,7 +9096,7 @@
         <v>7.2</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7163,7 +9104,7 @@
         <v>7.3</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7171,7 +9112,7 @@
         <v>7.4</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7179,7 +9120,7 @@
         <v>7.5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7187,7 +9128,7 @@
         <v>7.6</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7195,7 +9136,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7203,7 +9144,7 @@
         <v>8.1</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -7213,7 +9154,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.31496062992125984" bottom="0.31496062992125984" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;"Arial,Normal"&amp;10Página &amp;P de  &amp;N</oddFooter>
   </headerFooter>
@@ -7223,25 +9164,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="228" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="230"/>
+      <c r="A1" s="232" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="234"/>
       <c r="L1" s="72"/>
       <c r="M1" s="72"/>
       <c r="N1" s="73"/>

--- a/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aplicaciones Web\EData\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Inspecciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EData\Marcobre\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Inspecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569712BA-5368-491E-A890-D830887AFDF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B329CE-B416-48F9-88BF-EE501BF9B7B6}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="2" r:id="rId1"/>
+    <sheet name="Datos" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="Inspección" sheetId="1" r:id="rId2"/>
     <sheet name="Tablas" sheetId="3" r:id="rId3"/>
     <sheet name="Nivel Riesgo MA" sheetId="8" r:id="rId4"/>
@@ -24,9 +24,9 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LISTAFINAL">[1]Padrón!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Nivel Riesgo MA'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Nivel Riesgo SSO'!$A$1:$K$21</definedName>
+    <definedName name="LISTAFINAL">[1]Padrón!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -1955,6 +1955,147 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2000,12 +2141,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2069,132 +2204,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2230,15 +2239,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2630,7 +2630,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2951,7 +2951,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CA64"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="19" customWidth="1"/>
     <col min="2" max="2" width="14" style="19" customWidth="1"/>
@@ -4013,7 +4013,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF403"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="78" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" style="78" customWidth="1"/>
@@ -4051,129 +4051,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="189"/>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="191"/>
-      <c r="H1" s="169" t="s">
+      <c r="A1" s="178"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="214" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
-      <c r="Z1" s="170"/>
-      <c r="AA1" s="171"/>
-      <c r="AB1" s="160"/>
-      <c r="AC1" s="161"/>
-      <c r="AD1" s="161"/>
-      <c r="AE1" s="162"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
+      <c r="Z1" s="215"/>
+      <c r="AA1" s="216"/>
+      <c r="AB1" s="205"/>
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="207"/>
     </row>
     <row r="2" spans="1:32" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="192"/>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="193"/>
-      <c r="G2" s="194"/>
+      <c r="A2" s="181"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="183"/>
       <c r="H2" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="172" t="s">
+      <c r="I2" s="217" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="143" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="217"/>
+      <c r="M2" s="217"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="144"/>
-      <c r="R2" s="202">
+      <c r="Q2" s="191"/>
+      <c r="R2" s="188">
         <v>43831</v>
       </c>
-      <c r="S2" s="202"/>
-      <c r="T2" s="202"/>
-      <c r="U2" s="202"/>
-      <c r="V2" s="203"/>
+      <c r="S2" s="188"/>
+      <c r="T2" s="188"/>
+      <c r="U2" s="188"/>
+      <c r="V2" s="189"/>
       <c r="W2" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="X2" s="152" t="s">
+      <c r="X2" s="199" t="s">
         <v>215</v>
       </c>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="163"/>
-      <c r="AC2" s="164"/>
-      <c r="AD2" s="164"/>
-      <c r="AE2" s="165"/>
+      <c r="Y2" s="199"/>
+      <c r="Z2" s="199"/>
+      <c r="AA2" s="200"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="209"/>
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="210"/>
     </row>
     <row r="3" spans="1:32" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="195"/>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="197"/>
+      <c r="A3" s="184"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="186"/>
       <c r="H3" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="172" t="s">
+      <c r="I3" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="172"/>
-      <c r="M3" s="172"/>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="174" t="s">
+      <c r="J3" s="217"/>
+      <c r="K3" s="217"/>
+      <c r="L3" s="217"/>
+      <c r="M3" s="217"/>
+      <c r="N3" s="217"/>
+      <c r="O3" s="218"/>
+      <c r="P3" s="219" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="175"/>
-      <c r="R3" s="179">
+      <c r="Q3" s="220"/>
+      <c r="R3" s="224">
         <v>1</v>
       </c>
-      <c r="S3" s="179"/>
-      <c r="T3" s="179"/>
-      <c r="U3" s="179"/>
-      <c r="V3" s="180"/>
-      <c r="W3" s="150" t="s">
+      <c r="S3" s="224"/>
+      <c r="T3" s="224"/>
+      <c r="U3" s="224"/>
+      <c r="V3" s="225"/>
+      <c r="W3" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="151"/>
-      <c r="Y3" s="148">
+      <c r="X3" s="198"/>
+      <c r="Y3" s="195">
         <v>43800</v>
       </c>
-      <c r="Z3" s="148"/>
-      <c r="AA3" s="149"/>
-      <c r="AB3" s="166"/>
-      <c r="AC3" s="167"/>
-      <c r="AD3" s="167"/>
-      <c r="AE3" s="168"/>
+      <c r="Z3" s="195"/>
+      <c r="AA3" s="196"/>
+      <c r="AB3" s="211"/>
+      <c r="AC3" s="212"/>
+      <c r="AD3" s="212"/>
+      <c r="AE3" s="213"/>
     </row>
     <row r="4" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="80"/>
@@ -4208,39 +4208,39 @@
       <c r="AE4" s="130"/>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="187" t="s">
+      <c r="A5" s="176" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="188"/>
-      <c r="M5" s="188"/>
-      <c r="N5" s="188"/>
-      <c r="O5" s="188"/>
-      <c r="P5" s="188"/>
-      <c r="Q5" s="188"/>
-      <c r="R5" s="188"/>
-      <c r="S5" s="188"/>
-      <c r="T5" s="188"/>
-      <c r="U5" s="188"/>
-      <c r="V5" s="188"/>
-      <c r="W5" s="188"/>
-      <c r="X5" s="188"/>
-      <c r="Y5" s="188"/>
-      <c r="Z5" s="188"/>
-      <c r="AA5" s="188"/>
-      <c r="AB5" s="188"/>
-      <c r="AC5" s="188"/>
-      <c r="AD5" s="188"/>
-      <c r="AE5" s="198"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="177"/>
+      <c r="O5" s="177"/>
+      <c r="P5" s="177"/>
+      <c r="Q5" s="177"/>
+      <c r="R5" s="177"/>
+      <c r="S5" s="177"/>
+      <c r="T5" s="177"/>
+      <c r="U5" s="177"/>
+      <c r="V5" s="177"/>
+      <c r="W5" s="177"/>
+      <c r="X5" s="177"/>
+      <c r="Y5" s="177"/>
+      <c r="Z5" s="177"/>
+      <c r="AA5" s="177"/>
+      <c r="AB5" s="177"/>
+      <c r="AC5" s="177"/>
+      <c r="AD5" s="177"/>
+      <c r="AE5" s="187"/>
     </row>
     <row r="6" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="85"/>
@@ -4277,51 +4277,51 @@
     </row>
     <row r="7" spans="1:32" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="89"/>
-      <c r="B7" s="158" t="s">
+      <c r="B7" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="158"/>
-      <c r="D7" s="158"/>
-      <c r="E7" s="158"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="176" t="s">
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="177"/>
-      <c r="J7" s="178"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="223"/>
       <c r="K7" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="176">
+      <c r="L7" s="221">
         <v>20508972734</v>
       </c>
-      <c r="M7" s="177"/>
-      <c r="N7" s="178"/>
-      <c r="O7" s="157" t="s">
+      <c r="M7" s="222"/>
+      <c r="N7" s="223"/>
+      <c r="O7" s="204" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="159"/>
-      <c r="R7" s="154" t="s">
+      <c r="P7" s="170"/>
+      <c r="Q7" s="171"/>
+      <c r="R7" s="201" t="s">
         <v>25</v>
       </c>
-      <c r="S7" s="155"/>
-      <c r="T7" s="155"/>
-      <c r="U7" s="155"/>
-      <c r="V7" s="156"/>
+      <c r="S7" s="202"/>
+      <c r="T7" s="202"/>
+      <c r="U7" s="202"/>
+      <c r="V7" s="203"/>
       <c r="W7" s="90"/>
       <c r="X7" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" s="154" t="s">
+      <c r="Y7" s="201" t="s">
         <v>27</v>
       </c>
-      <c r="Z7" s="155"/>
-      <c r="AA7" s="155"/>
-      <c r="AB7" s="155"/>
-      <c r="AC7" s="155"/>
-      <c r="AD7" s="156"/>
+      <c r="Z7" s="202"/>
+      <c r="AA7" s="202"/>
+      <c r="AB7" s="202"/>
+      <c r="AC7" s="202"/>
+      <c r="AD7" s="203"/>
       <c r="AE7" s="91"/>
     </row>
     <row r="8" spans="1:32" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4390,39 +4390,39 @@
       <c r="AE9" s="99"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="187" t="s">
+      <c r="A10" s="176" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="188"/>
-      <c r="G10" s="188"/>
-      <c r="H10" s="188"/>
-      <c r="I10" s="188"/>
-      <c r="J10" s="188"/>
-      <c r="K10" s="188"/>
-      <c r="L10" s="188"/>
-      <c r="M10" s="188"/>
-      <c r="N10" s="188"/>
-      <c r="O10" s="188"/>
-      <c r="P10" s="188"/>
-      <c r="Q10" s="188"/>
-      <c r="R10" s="188"/>
-      <c r="S10" s="188"/>
-      <c r="T10" s="188"/>
-      <c r="U10" s="188"/>
-      <c r="V10" s="188"/>
-      <c r="W10" s="188"/>
-      <c r="X10" s="188"/>
-      <c r="Y10" s="188"/>
-      <c r="Z10" s="188"/>
-      <c r="AA10" s="188"/>
-      <c r="AB10" s="188"/>
-      <c r="AC10" s="188"/>
-      <c r="AD10" s="188"/>
-      <c r="AE10" s="198"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="177"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="177"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="177"/>
+      <c r="H10" s="177"/>
+      <c r="I10" s="177"/>
+      <c r="J10" s="177"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="177"/>
+      <c r="M10" s="177"/>
+      <c r="N10" s="177"/>
+      <c r="O10" s="177"/>
+      <c r="P10" s="177"/>
+      <c r="Q10" s="177"/>
+      <c r="R10" s="177"/>
+      <c r="S10" s="177"/>
+      <c r="T10" s="177"/>
+      <c r="U10" s="177"/>
+      <c r="V10" s="177"/>
+      <c r="W10" s="177"/>
+      <c r="X10" s="177"/>
+      <c r="Y10" s="177"/>
+      <c r="Z10" s="177"/>
+      <c r="AA10" s="177"/>
+      <c r="AB10" s="177"/>
+      <c r="AC10" s="177"/>
+      <c r="AD10" s="177"/>
+      <c r="AE10" s="187"/>
     </row>
     <row r="11" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="100"/>
@@ -4459,41 +4459,41 @@
     </row>
     <row r="12" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="89"/>
-      <c r="B12" s="215" t="s">
+      <c r="B12" s="151" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="215"/>
-      <c r="D12" s="215"/>
-      <c r="E12" s="215"/>
-      <c r="F12" s="215"/>
-      <c r="G12" s="216"/>
-      <c r="H12" s="211"/>
-      <c r="I12" s="217"/>
-      <c r="J12" s="217"/>
-      <c r="K12" s="217"/>
-      <c r="L12" s="212"/>
-      <c r="M12" s="222" t="s">
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="146"/>
+      <c r="M12" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="N12" s="206"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="199"/>
-      <c r="Q12" s="200"/>
-      <c r="R12" s="200"/>
-      <c r="S12" s="200"/>
-      <c r="T12" s="201"/>
-      <c r="U12" s="145" t="s">
+      <c r="N12" s="149"/>
+      <c r="O12" s="150"/>
+      <c r="P12" s="164"/>
+      <c r="Q12" s="165"/>
+      <c r="R12" s="165"/>
+      <c r="S12" s="165"/>
+      <c r="T12" s="166"/>
+      <c r="U12" s="192" t="s">
         <v>218</v>
       </c>
-      <c r="V12" s="146"/>
-      <c r="W12" s="146"/>
-      <c r="X12" s="147"/>
-      <c r="Y12" s="235"/>
-      <c r="Z12" s="236"/>
-      <c r="AA12" s="236"/>
-      <c r="AB12" s="236"/>
-      <c r="AC12" s="236"/>
-      <c r="AD12" s="237"/>
+      <c r="V12" s="193"/>
+      <c r="W12" s="193"/>
+      <c r="X12" s="194"/>
+      <c r="Y12" s="147"/>
+      <c r="Z12" s="159"/>
+      <c r="AA12" s="159"/>
+      <c r="AB12" s="159"/>
+      <c r="AC12" s="159"/>
+      <c r="AD12" s="148"/>
       <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -4531,43 +4531,43 @@
     </row>
     <row r="14" spans="1:32" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="89"/>
-      <c r="B14" s="204" t="s">
+      <c r="B14" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="218"/>
-      <c r="J14" s="218"/>
-      <c r="K14" s="218"/>
-      <c r="L14" s="214"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="158"/>
+      <c r="H14" s="154"/>
+      <c r="I14" s="155"/>
+      <c r="J14" s="155"/>
+      <c r="K14" s="155"/>
+      <c r="L14" s="156"/>
       <c r="M14" s="106"/>
       <c r="N14" s="106"/>
       <c r="O14" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="P14" s="211"/>
-      <c r="Q14" s="212"/>
+      <c r="P14" s="145"/>
+      <c r="Q14" s="146"/>
       <c r="R14" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="S14" s="235"/>
-      <c r="T14" s="237"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="148"/>
       <c r="U14" s="125"/>
-      <c r="V14" s="206" t="s">
+      <c r="V14" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="W14" s="206"/>
-      <c r="X14" s="207"/>
-      <c r="Y14" s="219"/>
-      <c r="Z14" s="220"/>
-      <c r="AA14" s="220"/>
-      <c r="AB14" s="220"/>
-      <c r="AC14" s="220"/>
-      <c r="AD14" s="221"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="150"/>
+      <c r="Y14" s="160"/>
+      <c r="Z14" s="161"/>
+      <c r="AA14" s="161"/>
+      <c r="AB14" s="161"/>
+      <c r="AC14" s="161"/>
+      <c r="AD14" s="162"/>
       <c r="AE14" s="110"/>
       <c r="AF14" s="111"/>
     </row>
@@ -4606,43 +4606,43 @@
     </row>
     <row r="16" spans="1:32" ht="49.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="89"/>
-      <c r="B16" s="204" t="s">
+      <c r="B16" s="157" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="205"/>
-      <c r="H16" s="199"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="201"/>
-      <c r="M16" s="208" t="s">
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="164"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="165"/>
+      <c r="K16" s="165"/>
+      <c r="L16" s="166"/>
+      <c r="M16" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="209"/>
-      <c r="O16" s="210"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="144"/>
       <c r="P16" s="114"/>
       <c r="Q16" s="114"/>
       <c r="R16" s="114"/>
-      <c r="S16" s="206" t="s">
+      <c r="S16" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="T16" s="206"/>
-      <c r="U16" s="206"/>
-      <c r="V16" s="206"/>
-      <c r="W16" s="206"/>
-      <c r="X16" s="207"/>
-      <c r="Y16" s="199"/>
-      <c r="Z16" s="200"/>
-      <c r="AA16" s="200"/>
-      <c r="AB16" s="201"/>
-      <c r="AC16" s="208" t="s">
+      <c r="T16" s="149"/>
+      <c r="U16" s="149"/>
+      <c r="V16" s="149"/>
+      <c r="W16" s="149"/>
+      <c r="X16" s="150"/>
+      <c r="Y16" s="164"/>
+      <c r="Z16" s="165"/>
+      <c r="AA16" s="165"/>
+      <c r="AB16" s="166"/>
+      <c r="AC16" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="AD16" s="210"/>
+      <c r="AD16" s="144"/>
       <c r="AE16" s="115"/>
     </row>
     <row r="17" spans="1:31" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -4680,37 +4680,37 @@
     </row>
     <row r="18" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="89"/>
-      <c r="B18" s="204" t="s">
+      <c r="B18" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="204"/>
-      <c r="D18" s="204"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="205"/>
-      <c r="H18" s="199"/>
-      <c r="I18" s="200"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="200"/>
-      <c r="L18" s="200"/>
-      <c r="M18" s="200"/>
-      <c r="N18" s="200"/>
-      <c r="O18" s="200"/>
-      <c r="P18" s="200"/>
-      <c r="Q18" s="200"/>
-      <c r="R18" s="200"/>
-      <c r="S18" s="200"/>
-      <c r="T18" s="200"/>
-      <c r="U18" s="200"/>
-      <c r="V18" s="200"/>
-      <c r="W18" s="200"/>
-      <c r="X18" s="200"/>
-      <c r="Y18" s="200"/>
-      <c r="Z18" s="200"/>
-      <c r="AA18" s="200"/>
-      <c r="AB18" s="200"/>
-      <c r="AC18" s="200"/>
-      <c r="AD18" s="201"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="164"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="165"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="165"/>
+      <c r="Q18" s="165"/>
+      <c r="R18" s="165"/>
+      <c r="S18" s="165"/>
+      <c r="T18" s="165"/>
+      <c r="U18" s="165"/>
+      <c r="V18" s="165"/>
+      <c r="W18" s="165"/>
+      <c r="X18" s="165"/>
+      <c r="Y18" s="165"/>
+      <c r="Z18" s="165"/>
+      <c r="AA18" s="165"/>
+      <c r="AB18" s="165"/>
+      <c r="AC18" s="165"/>
+      <c r="AD18" s="166"/>
       <c r="AE18" s="116"/>
     </row>
     <row r="19" spans="1:31" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4751,43 +4751,43 @@
       <c r="C20" s="111"/>
       <c r="D20" s="124"/>
       <c r="E20" s="124"/>
-      <c r="F20" s="200"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="200"/>
-      <c r="I20" s="200"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="200"/>
-      <c r="L20" s="200"/>
-      <c r="M20" s="200"/>
-      <c r="N20" s="200"/>
-      <c r="O20" s="200"/>
-      <c r="P20" s="200"/>
-      <c r="Q20" s="200"/>
-      <c r="R20" s="200"/>
-      <c r="S20" s="200"/>
-      <c r="T20" s="200"/>
-      <c r="U20" s="200"/>
-      <c r="V20" s="200"/>
-      <c r="W20" s="200"/>
-      <c r="X20" s="200"/>
-      <c r="Y20" s="200"/>
-      <c r="Z20" s="200"/>
-      <c r="AA20" s="200"/>
-      <c r="AB20" s="200"/>
-      <c r="AC20" s="200"/>
-      <c r="AD20" s="200"/>
-      <c r="AE20" s="200"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
+      <c r="L20" s="165"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="165"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="165"/>
+      <c r="R20" s="165"/>
+      <c r="S20" s="165"/>
+      <c r="T20" s="165"/>
+      <c r="U20" s="165"/>
+      <c r="V20" s="165"/>
+      <c r="W20" s="165"/>
+      <c r="X20" s="165"/>
+      <c r="Y20" s="165"/>
+      <c r="Z20" s="165"/>
+      <c r="AA20" s="165"/>
+      <c r="AB20" s="165"/>
+      <c r="AC20" s="165"/>
+      <c r="AD20" s="165"/>
+      <c r="AE20" s="165"/>
     </row>
     <row r="21" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="187" t="s">
+      <c r="A21" s="176" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="188"/>
-      <c r="C21" s="188"/>
-      <c r="D21" s="188"/>
-      <c r="E21" s="188"/>
-      <c r="F21" s="188"/>
-      <c r="G21" s="188"/>
+      <c r="B21" s="177"/>
+      <c r="C21" s="177"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="177"/>
+      <c r="G21" s="177"/>
       <c r="H21" s="120"/>
       <c r="I21" s="120"/>
       <c r="J21" s="120"/>
@@ -4814,92 +4814,92 @@
       <c r="AE21" s="121"/>
     </row>
     <row r="22" spans="1:31" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
-      <c r="B22" s="182"/>
-      <c r="C22" s="182"/>
-      <c r="D22" s="182"/>
-      <c r="E22" s="182"/>
-      <c r="F22" s="182"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="182"/>
-      <c r="I22" s="182"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="182"/>
-      <c r="Q22" s="182"/>
-      <c r="R22" s="182"/>
-      <c r="S22" s="182"/>
-      <c r="T22" s="182"/>
-      <c r="U22" s="182"/>
-      <c r="V22" s="182"/>
-      <c r="W22" s="182"/>
-      <c r="X22" s="182"/>
-      <c r="Y22" s="182"/>
-      <c r="Z22" s="182"/>
-      <c r="AA22" s="182"/>
-      <c r="AB22" s="182"/>
-      <c r="AC22" s="182"/>
-      <c r="AD22" s="182"/>
-      <c r="AE22" s="183"/>
+      <c r="A22" s="173"/>
+      <c r="B22" s="174"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="174"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="174"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="174"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
+      <c r="V22" s="174"/>
+      <c r="W22" s="174"/>
+      <c r="X22" s="174"/>
+      <c r="Y22" s="174"/>
+      <c r="Z22" s="174"/>
+      <c r="AA22" s="174"/>
+      <c r="AB22" s="174"/>
+      <c r="AC22" s="174"/>
+      <c r="AD22" s="174"/>
+      <c r="AE22" s="175"/>
     </row>
     <row r="23" spans="1:31" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="184" t="s">
+      <c r="A23" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="186"/>
+      <c r="B23" s="169"/>
       <c r="C23" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="184" t="s">
+      <c r="D23" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="185"/>
-      <c r="I23" s="186"/>
-      <c r="J23" s="184" t="s">
+      <c r="E23" s="168"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="168"/>
+      <c r="H23" s="168"/>
+      <c r="I23" s="169"/>
+      <c r="J23" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="185"/>
-      <c r="L23" s="185"/>
-      <c r="M23" s="185"/>
-      <c r="N23" s="186"/>
-      <c r="O23" s="184" t="s">
+      <c r="K23" s="168"/>
+      <c r="L23" s="168"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="169"/>
+      <c r="O23" s="167" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="185"/>
-      <c r="Q23" s="186"/>
+      <c r="P23" s="168"/>
+      <c r="Q23" s="169"/>
       <c r="R23" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="184" t="s">
+      <c r="S23" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="T23" s="185"/>
-      <c r="U23" s="185"/>
-      <c r="V23" s="185"/>
-      <c r="W23" s="186"/>
+      <c r="T23" s="168"/>
+      <c r="U23" s="168"/>
+      <c r="V23" s="168"/>
+      <c r="W23" s="169"/>
       <c r="X23" s="122" t="s">
         <v>15</v>
       </c>
       <c r="Y23" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="Z23" s="184" t="s">
+      <c r="Z23" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="AA23" s="185"/>
-      <c r="AB23" s="185"/>
-      <c r="AC23" s="186"/>
-      <c r="AD23" s="184" t="s">
+      <c r="AA23" s="168"/>
+      <c r="AB23" s="168"/>
+      <c r="AC23" s="169"/>
+      <c r="AD23" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="AE23" s="186"/>
+      <c r="AE23" s="169"/>
     </row>
     <row r="24" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="142"/>
@@ -7099,27 +7099,19 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="50">
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="Y12:AD12"/>
-    <mergeCell ref="Y14:AD14"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="J23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="S23:W23"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="A22:AE22"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="Y7:AD7"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="AB1:AE3"/>
+    <mergeCell ref="H1:AA1"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A5:AE5"/>
     <mergeCell ref="A10:AE10"/>
@@ -7136,19 +7128,27 @@
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="U12:X12"/>
     <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="Y7:AD7"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="AB1:AE3"/>
-    <mergeCell ref="H1:AA1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="J23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="A22:AE22"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="Y12:AD12"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="H16:L16"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.35433070866141736" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -7191,7 +7191,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="44.5546875" customWidth="1"/>
     <col min="3" max="3" width="5.5546875" customWidth="1"/>
@@ -7199,14 +7199,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="226" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="224"/>
-      <c r="D1" s="223" t="s">
+      <c r="B1" s="227"/>
+      <c r="D1" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="224"/>
+      <c r="E1" s="227"/>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -7499,7 +7499,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK38"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="34" customWidth="1"/>
     <col min="2" max="2" width="7.6640625" style="34" customWidth="1"/>
@@ -8024,20 +8024,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="230"/>
+      <c r="B1" s="232"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="233"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="225" t="s">
+      <c r="A2" s="228" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="226"/>
-      <c r="C2" s="226"/>
-      <c r="D2" s="227"/>
+      <c r="B2" s="229"/>
+      <c r="C2" s="229"/>
+      <c r="D2" s="230"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
@@ -8067,7 +8067,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
         <v>127</v>
       </c>
@@ -8104,12 +8104,12 @@
       <c r="D7" s="52"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="225" t="s">
+      <c r="A8" s="228" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="227"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
     </row>
     <row r="9" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
@@ -8176,12 +8176,12 @@
       <c r="H13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="225" t="s">
+      <c r="A14" s="228" t="s">
         <v>214</v>
       </c>
-      <c r="B14" s="226"/>
-      <c r="C14" s="226"/>
-      <c r="D14" s="227"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="230"/>
     </row>
     <row r="15" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49"/>
@@ -8720,7 +8720,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.31496062992125984" bottom="0.31496062992125984" header="0.15748031496062992" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="68" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
@@ -8734,7 +8734,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="109" style="1" customWidth="1"/>
@@ -8742,10 +8742,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="234" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="231"/>
+      <c r="B1" s="234"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
@@ -9154,7 +9154,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.31496062992125984" bottom="0.31496062992125984" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;"Arial,Normal"&amp;10Página &amp;P de  &amp;N</oddFooter>
   </headerFooter>
@@ -9164,25 +9164,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="232" t="s">
+      <c r="A1" s="235" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="237"/>
       <c r="L1" s="72"/>
       <c r="M1" s="72"/>
       <c r="N1" s="73"/>

--- a/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/Inspecciones/JU-MAP-PRO-004.F01_Inspección_V00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electrodata\Marcobre\Rediseño\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Inspecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526ED734-5008-419E-BC16-01F97C131F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB8950F-B42C-4822-B642-C7069D3673DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14010" yWindow="5490" windowWidth="28800" windowHeight="15435" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="2" state="hidden" r:id="rId1"/>
@@ -1186,14 +1186,14 @@
     <t>Responsable del Registro:</t>
   </si>
   <si>
-    <t>KARLA MONTOYA / CARLOS CUBAS</t>
-  </si>
-  <si>
     <t>Acción preventiva/correctiva
 (conclusiones y cecomendaciones)</t>
   </si>
   <si>
     <t>Descripción de Condición/Acto Subestándar</t>
+  </si>
+  <si>
+    <t>KARLA MONTOYA</t>
   </si>
 </sst>
 </file>
@@ -1968,6 +1968,168 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1992,12 +2154,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2061,153 +2217,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2243,15 +2252,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4064,129 +4064,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175"/>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="163" t="s">
+      <c r="A1" s="179"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
-      <c r="M1" s="164"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="164"/>
-      <c r="P1" s="164"/>
-      <c r="Q1" s="164"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="164"/>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="164"/>
-      <c r="AA1" s="165"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="155"/>
-      <c r="AE1" s="156"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="216"/>
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="216"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="206"/>
+      <c r="AC1" s="207"/>
+      <c r="AD1" s="207"/>
+      <c r="AE1" s="208"/>
     </row>
     <row r="2" spans="1:32" ht="29.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="178"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="180"/>
+      <c r="A2" s="182"/>
+      <c r="B2" s="183"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="184"/>
       <c r="H2" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="166" t="s">
+      <c r="I2" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="199" t="s">
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="219"/>
+      <c r="P2" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="200"/>
-      <c r="R2" s="193">
+      <c r="Q2" s="192"/>
+      <c r="R2" s="189">
         <v>43831</v>
       </c>
-      <c r="S2" s="193"/>
-      <c r="T2" s="193"/>
-      <c r="U2" s="193"/>
-      <c r="V2" s="194"/>
+      <c r="S2" s="189"/>
+      <c r="T2" s="189"/>
+      <c r="U2" s="189"/>
+      <c r="V2" s="190"/>
       <c r="W2" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="146" t="s">
+      <c r="X2" s="200" t="s">
         <v>213</v>
       </c>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="147"/>
-      <c r="AB2" s="157"/>
-      <c r="AC2" s="158"/>
-      <c r="AD2" s="158"/>
-      <c r="AE2" s="159"/>
+      <c r="Y2" s="200"/>
+      <c r="Z2" s="200"/>
+      <c r="AA2" s="201"/>
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="210"/>
+      <c r="AD2" s="210"/>
+      <c r="AE2" s="211"/>
     </row>
     <row r="3" spans="1:32" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="181"/>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="183"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="186"/>
+      <c r="D3" s="186"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="187"/>
       <c r="H3" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="166" t="s">
+      <c r="I3" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="168" t="s">
+      <c r="J3" s="218"/>
+      <c r="K3" s="218"/>
+      <c r="L3" s="218"/>
+      <c r="M3" s="218"/>
+      <c r="N3" s="218"/>
+      <c r="O3" s="219"/>
+      <c r="P3" s="220" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="173">
+      <c r="Q3" s="221"/>
+      <c r="R3" s="225">
         <v>1</v>
       </c>
-      <c r="S3" s="173"/>
-      <c r="T3" s="173"/>
-      <c r="U3" s="173"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="144" t="s">
+      <c r="S3" s="225"/>
+      <c r="T3" s="225"/>
+      <c r="U3" s="225"/>
+      <c r="V3" s="226"/>
+      <c r="W3" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="X3" s="145"/>
-      <c r="Y3" s="204">
+      <c r="X3" s="199"/>
+      <c r="Y3" s="196">
         <v>43800</v>
       </c>
-      <c r="Z3" s="204"/>
-      <c r="AA3" s="205"/>
-      <c r="AB3" s="160"/>
-      <c r="AC3" s="161"/>
-      <c r="AD3" s="161"/>
-      <c r="AE3" s="162"/>
+      <c r="Z3" s="196"/>
+      <c r="AA3" s="197"/>
+      <c r="AB3" s="212"/>
+      <c r="AC3" s="213"/>
+      <c r="AD3" s="213"/>
+      <c r="AE3" s="214"/>
     </row>
     <row r="4" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="80"/>
@@ -4221,39 +4221,39 @@
       <c r="AE4" s="143"/>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="s">
+      <c r="A5" s="169" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="185"/>
-      <c r="N5" s="185"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="185"/>
-      <c r="Q5" s="185"/>
-      <c r="R5" s="185"/>
-      <c r="S5" s="185"/>
-      <c r="T5" s="185"/>
-      <c r="U5" s="185"/>
-      <c r="V5" s="185"/>
-      <c r="W5" s="185"/>
-      <c r="X5" s="185"/>
-      <c r="Y5" s="185"/>
-      <c r="Z5" s="185"/>
-      <c r="AA5" s="185"/>
-      <c r="AB5" s="185"/>
-      <c r="AC5" s="185"/>
-      <c r="AD5" s="185"/>
-      <c r="AE5" s="186"/>
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="170"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="170"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="170"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="170"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="170"/>
+      <c r="U5" s="170"/>
+      <c r="V5" s="170"/>
+      <c r="W5" s="170"/>
+      <c r="X5" s="170"/>
+      <c r="Y5" s="170"/>
+      <c r="Z5" s="170"/>
+      <c r="AA5" s="170"/>
+      <c r="AB5" s="170"/>
+      <c r="AC5" s="170"/>
+      <c r="AD5" s="170"/>
+      <c r="AE5" s="188"/>
     </row>
     <row r="6" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="85"/>
@@ -4290,51 +4290,51 @@
     </row>
     <row r="7" spans="1:32" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="89"/>
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="170" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="222" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="171"/>
-      <c r="J7" s="172"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="224"/>
       <c r="K7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="170">
+      <c r="L7" s="222">
         <v>20508972734</v>
       </c>
-      <c r="M7" s="171"/>
-      <c r="N7" s="172"/>
-      <c r="O7" s="151" t="s">
+      <c r="M7" s="223"/>
+      <c r="N7" s="224"/>
+      <c r="O7" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="P7" s="152"/>
-      <c r="Q7" s="153"/>
-      <c r="R7" s="148" t="s">
+      <c r="P7" s="164"/>
+      <c r="Q7" s="165"/>
+      <c r="R7" s="202" t="s">
         <v>23</v>
       </c>
-      <c r="S7" s="149"/>
-      <c r="T7" s="149"/>
-      <c r="U7" s="149"/>
-      <c r="V7" s="150"/>
+      <c r="S7" s="203"/>
+      <c r="T7" s="203"/>
+      <c r="U7" s="203"/>
+      <c r="V7" s="204"/>
       <c r="W7" s="90"/>
       <c r="X7" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="Y7" s="148" t="s">
+      <c r="Y7" s="202" t="s">
         <v>25</v>
       </c>
-      <c r="Z7" s="149"/>
-      <c r="AA7" s="149"/>
-      <c r="AB7" s="149"/>
-      <c r="AC7" s="149"/>
-      <c r="AD7" s="150"/>
+      <c r="Z7" s="203"/>
+      <c r="AA7" s="203"/>
+      <c r="AB7" s="203"/>
+      <c r="AC7" s="203"/>
+      <c r="AD7" s="204"/>
       <c r="AE7" s="91"/>
     </row>
     <row r="8" spans="1:32" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4403,39 +4403,39 @@
       <c r="AE9" s="99"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="184" t="s">
+      <c r="A10" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="185"/>
-      <c r="C10" s="185"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
-      <c r="N10" s="185"/>
-      <c r="O10" s="185"/>
-      <c r="P10" s="185"/>
-      <c r="Q10" s="185"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="186"/>
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="170"/>
+      <c r="H10" s="170"/>
+      <c r="I10" s="170"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="170"/>
+      <c r="L10" s="170"/>
+      <c r="M10" s="170"/>
+      <c r="N10" s="170"/>
+      <c r="O10" s="170"/>
+      <c r="P10" s="170"/>
+      <c r="Q10" s="170"/>
+      <c r="R10" s="170"/>
+      <c r="S10" s="170"/>
+      <c r="T10" s="170"/>
+      <c r="U10" s="170"/>
+      <c r="V10" s="170"/>
+      <c r="W10" s="170"/>
+      <c r="X10" s="170"/>
+      <c r="Y10" s="170"/>
+      <c r="Z10" s="170"/>
+      <c r="AA10" s="170"/>
+      <c r="AB10" s="170"/>
+      <c r="AC10" s="170"/>
+      <c r="AD10" s="170"/>
+      <c r="AE10" s="188"/>
     </row>
     <row r="11" spans="1:32" s="88" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="100"/>
@@ -4472,41 +4472,41 @@
     </row>
     <row r="12" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="89"/>
-      <c r="B12" s="213" t="s">
+      <c r="B12" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="C12" s="213"/>
-      <c r="D12" s="213"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="214"/>
-      <c r="H12" s="209"/>
-      <c r="I12" s="215"/>
-      <c r="J12" s="215"/>
-      <c r="K12" s="215"/>
-      <c r="L12" s="210"/>
-      <c r="M12" s="223" t="s">
+      <c r="C12" s="173"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="171"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="197"/>
-      <c r="O12" s="198"/>
-      <c r="P12" s="189"/>
-      <c r="Q12" s="190"/>
-      <c r="R12" s="190"/>
-      <c r="S12" s="190"/>
-      <c r="T12" s="191"/>
-      <c r="U12" s="201" t="s">
+      <c r="N12" s="159"/>
+      <c r="O12" s="160"/>
+      <c r="P12" s="161"/>
+      <c r="Q12" s="162"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="162"/>
+      <c r="T12" s="163"/>
+      <c r="U12" s="193" t="s">
         <v>216</v>
       </c>
-      <c r="V12" s="202"/>
-      <c r="W12" s="202"/>
-      <c r="X12" s="203"/>
-      <c r="Y12" s="211"/>
-      <c r="Z12" s="219"/>
-      <c r="AA12" s="219"/>
-      <c r="AB12" s="219"/>
-      <c r="AC12" s="219"/>
-      <c r="AD12" s="212"/>
+      <c r="V12" s="194"/>
+      <c r="W12" s="194"/>
+      <c r="X12" s="195"/>
+      <c r="Y12" s="152"/>
+      <c r="Z12" s="153"/>
+      <c r="AA12" s="153"/>
+      <c r="AB12" s="153"/>
+      <c r="AC12" s="153"/>
+      <c r="AD12" s="154"/>
       <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
@@ -4544,43 +4544,43 @@
     </row>
     <row r="14" spans="1:32" ht="28.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="89"/>
-      <c r="B14" s="195" t="s">
+      <c r="B14" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
-      <c r="F14" s="195"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="216"/>
-      <c r="I14" s="217"/>
-      <c r="J14" s="217"/>
-      <c r="K14" s="217"/>
-      <c r="L14" s="218"/>
+      <c r="C14" s="147"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="177"/>
+      <c r="J14" s="177"/>
+      <c r="K14" s="177"/>
+      <c r="L14" s="178"/>
       <c r="M14" s="106"/>
       <c r="N14" s="106"/>
       <c r="O14" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="210"/>
+      <c r="P14" s="171"/>
+      <c r="Q14" s="172"/>
       <c r="R14" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="S14" s="211"/>
-      <c r="T14" s="212"/>
+      <c r="S14" s="152"/>
+      <c r="T14" s="154"/>
       <c r="U14" s="139"/>
-      <c r="V14" s="197" t="s">
+      <c r="V14" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="W14" s="197"/>
-      <c r="X14" s="198"/>
-      <c r="Y14" s="220"/>
-      <c r="Z14" s="221"/>
-      <c r="AA14" s="221"/>
-      <c r="AB14" s="221"/>
-      <c r="AC14" s="221"/>
-      <c r="AD14" s="222"/>
+      <c r="W14" s="159"/>
+      <c r="X14" s="160"/>
+      <c r="Y14" s="155"/>
+      <c r="Z14" s="156"/>
+      <c r="AA14" s="156"/>
+      <c r="AB14" s="156"/>
+      <c r="AC14" s="156"/>
+      <c r="AD14" s="157"/>
       <c r="AE14" s="110"/>
       <c r="AF14" s="111"/>
     </row>
@@ -4619,39 +4619,39 @@
     </row>
     <row r="16" spans="1:32" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="89"/>
-      <c r="B16" s="195" t="s">
+      <c r="B16" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="195"/>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
-      <c r="F16" s="195"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="190"/>
-      <c r="J16" s="190"/>
-      <c r="K16" s="190"/>
-      <c r="L16" s="190"/>
-      <c r="M16" s="190"/>
-      <c r="N16" s="190"/>
-      <c r="O16" s="191"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="162"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="163"/>
       <c r="P16" s="114"/>
       <c r="Q16" s="114"/>
       <c r="R16" s="114"/>
-      <c r="S16" s="197" t="s">
+      <c r="S16" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="T16" s="197"/>
-      <c r="U16" s="197"/>
-      <c r="V16" s="197"/>
-      <c r="W16" s="197"/>
-      <c r="X16" s="198"/>
-      <c r="Y16" s="189"/>
-      <c r="Z16" s="190"/>
-      <c r="AA16" s="190"/>
-      <c r="AB16" s="190"/>
-      <c r="AC16" s="190"/>
-      <c r="AD16" s="191"/>
+      <c r="T16" s="159"/>
+      <c r="U16" s="159"/>
+      <c r="V16" s="159"/>
+      <c r="W16" s="159"/>
+      <c r="X16" s="160"/>
+      <c r="Y16" s="161"/>
+      <c r="Z16" s="162"/>
+      <c r="AA16" s="162"/>
+      <c r="AB16" s="162"/>
+      <c r="AC16" s="162"/>
+      <c r="AD16" s="163"/>
       <c r="AE16" s="115"/>
     </row>
     <row r="17" spans="1:31" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
@@ -4689,37 +4689,37 @@
     </row>
     <row r="18" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="89"/>
-      <c r="B18" s="195" t="s">
+      <c r="B18" s="147" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="195"/>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="195"/>
-      <c r="G18" s="196"/>
-      <c r="H18" s="189"/>
-      <c r="I18" s="190"/>
-      <c r="J18" s="190"/>
-      <c r="K18" s="190"/>
-      <c r="L18" s="190"/>
-      <c r="M18" s="190"/>
-      <c r="N18" s="190"/>
-      <c r="O18" s="190"/>
-      <c r="P18" s="190"/>
-      <c r="Q18" s="190"/>
-      <c r="R18" s="190"/>
-      <c r="S18" s="190"/>
-      <c r="T18" s="190"/>
-      <c r="U18" s="190"/>
-      <c r="V18" s="190"/>
-      <c r="W18" s="190"/>
-      <c r="X18" s="190"/>
-      <c r="Y18" s="190"/>
-      <c r="Z18" s="190"/>
-      <c r="AA18" s="190"/>
-      <c r="AB18" s="190"/>
-      <c r="AC18" s="190"/>
-      <c r="AD18" s="191"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="162"/>
+      <c r="K18" s="162"/>
+      <c r="L18" s="162"/>
+      <c r="M18" s="162"/>
+      <c r="N18" s="162"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="162"/>
+      <c r="Q18" s="162"/>
+      <c r="R18" s="162"/>
+      <c r="S18" s="162"/>
+      <c r="T18" s="162"/>
+      <c r="U18" s="162"/>
+      <c r="V18" s="162"/>
+      <c r="W18" s="162"/>
+      <c r="X18" s="162"/>
+      <c r="Y18" s="162"/>
+      <c r="Z18" s="162"/>
+      <c r="AA18" s="162"/>
+      <c r="AB18" s="162"/>
+      <c r="AC18" s="162"/>
+      <c r="AD18" s="163"/>
       <c r="AE18" s="116"/>
     </row>
     <row r="19" spans="1:31" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
@@ -4757,39 +4757,39 @@
     </row>
     <row r="20" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="89"/>
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
-      <c r="F20" s="195"/>
-      <c r="G20" s="196"/>
-      <c r="H20" s="236" t="s">
-        <v>289</v>
-      </c>
-      <c r="I20" s="237"/>
-      <c r="J20" s="237"/>
-      <c r="K20" s="237"/>
-      <c r="L20" s="237"/>
-      <c r="M20" s="237"/>
-      <c r="N20" s="237"/>
-      <c r="O20" s="237"/>
-      <c r="P20" s="237"/>
-      <c r="Q20" s="237"/>
-      <c r="R20" s="237"/>
-      <c r="S20" s="237"/>
-      <c r="T20" s="237"/>
-      <c r="U20" s="237"/>
-      <c r="V20" s="237"/>
-      <c r="W20" s="237"/>
-      <c r="X20" s="237"/>
-      <c r="Y20" s="237"/>
-      <c r="Z20" s="237"/>
-      <c r="AA20" s="237"/>
-      <c r="AB20" s="237"/>
-      <c r="AC20" s="237"/>
-      <c r="AD20" s="238"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="147"/>
+      <c r="G20" s="148"/>
+      <c r="H20" s="144" t="s">
+        <v>291</v>
+      </c>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
+      <c r="U20" s="145"/>
+      <c r="V20" s="145"/>
+      <c r="W20" s="145"/>
+      <c r="X20" s="145"/>
+      <c r="Y20" s="145"/>
+      <c r="Z20" s="145"/>
+      <c r="AA20" s="145"/>
+      <c r="AB20" s="145"/>
+      <c r="AC20" s="145"/>
+      <c r="AD20" s="146"/>
       <c r="AE20" s="116"/>
     </row>
     <row r="21" spans="1:31" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4830,43 +4830,43 @@
       <c r="C22" s="111"/>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
-      <c r="F22" s="190"/>
-      <c r="G22" s="190"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
-      <c r="K22" s="190"/>
-      <c r="L22" s="190"/>
-      <c r="M22" s="190"/>
-      <c r="N22" s="190"/>
-      <c r="O22" s="190"/>
-      <c r="P22" s="190"/>
-      <c r="Q22" s="190"/>
-      <c r="R22" s="190"/>
-      <c r="S22" s="190"/>
-      <c r="T22" s="190"/>
-      <c r="U22" s="190"/>
-      <c r="V22" s="190"/>
-      <c r="W22" s="190"/>
-      <c r="X22" s="190"/>
-      <c r="Y22" s="190"/>
-      <c r="Z22" s="190"/>
-      <c r="AA22" s="190"/>
-      <c r="AB22" s="190"/>
-      <c r="AC22" s="190"/>
-      <c r="AD22" s="190"/>
-      <c r="AE22" s="190"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="162"/>
+      <c r="Q22" s="162"/>
+      <c r="R22" s="162"/>
+      <c r="S22" s="162"/>
+      <c r="T22" s="162"/>
+      <c r="U22" s="162"/>
+      <c r="V22" s="162"/>
+      <c r="W22" s="162"/>
+      <c r="X22" s="162"/>
+      <c r="Y22" s="162"/>
+      <c r="Z22" s="162"/>
+      <c r="AA22" s="162"/>
+      <c r="AB22" s="162"/>
+      <c r="AC22" s="162"/>
+      <c r="AD22" s="162"/>
+      <c r="AE22" s="162"/>
     </row>
     <row r="23" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="184" t="s">
+      <c r="A23" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="185"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
+      <c r="B23" s="170"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="170"/>
       <c r="H23" s="120"/>
       <c r="I23" s="120"/>
       <c r="J23" s="120"/>
@@ -4893,94 +4893,94 @@
       <c r="AE23" s="121"/>
     </row>
     <row r="24" spans="1:31" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="206"/>
-      <c r="B24" s="207"/>
-      <c r="C24" s="207"/>
-      <c r="D24" s="207"/>
-      <c r="E24" s="207"/>
-      <c r="F24" s="207"/>
-      <c r="G24" s="207"/>
-      <c r="H24" s="207"/>
-      <c r="I24" s="207"/>
-      <c r="J24" s="207"/>
-      <c r="K24" s="207"/>
-      <c r="L24" s="207"/>
-      <c r="M24" s="207"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="207"/>
-      <c r="P24" s="207"/>
-      <c r="Q24" s="207"/>
-      <c r="R24" s="207"/>
-      <c r="S24" s="207"/>
-      <c r="T24" s="207"/>
-      <c r="U24" s="207"/>
-      <c r="V24" s="207"/>
-      <c r="W24" s="207"/>
-      <c r="X24" s="207"/>
-      <c r="Y24" s="207"/>
-      <c r="Z24" s="207"/>
-      <c r="AA24" s="207"/>
-      <c r="AB24" s="207"/>
-      <c r="AC24" s="207"/>
-      <c r="AD24" s="207"/>
-      <c r="AE24" s="208"/>
+      <c r="A24" s="166"/>
+      <c r="B24" s="167"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="167"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="167"/>
+      <c r="O24" s="167"/>
+      <c r="P24" s="167"/>
+      <c r="Q24" s="167"/>
+      <c r="R24" s="167"/>
+      <c r="S24" s="167"/>
+      <c r="T24" s="167"/>
+      <c r="U24" s="167"/>
+      <c r="V24" s="167"/>
+      <c r="W24" s="167"/>
+      <c r="X24" s="167"/>
+      <c r="Y24" s="167"/>
+      <c r="Z24" s="167"/>
+      <c r="AA24" s="167"/>
+      <c r="AB24" s="167"/>
+      <c r="AC24" s="167"/>
+      <c r="AD24" s="167"/>
+      <c r="AE24" s="168"/>
     </row>
     <row r="25" spans="1:31" ht="52.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="187" t="s">
+      <c r="A25" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="188"/>
+      <c r="B25" s="151"/>
       <c r="C25" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="187" t="s">
+      <c r="D25" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="192"/>
-      <c r="F25" s="192"/>
-      <c r="G25" s="192"/>
-      <c r="H25" s="192"/>
-      <c r="I25" s="188"/>
-      <c r="J25" s="187" t="s">
+      <c r="E25" s="150"/>
+      <c r="F25" s="150"/>
+      <c r="G25" s="150"/>
+      <c r="H25" s="150"/>
+      <c r="I25" s="151"/>
+      <c r="J25" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="K25" s="192"/>
-      <c r="L25" s="187" t="s">
+      <c r="K25" s="150"/>
+      <c r="L25" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="192"/>
-      <c r="N25" s="188"/>
-      <c r="O25" s="187" t="s">
-        <v>291</v>
-      </c>
-      <c r="P25" s="192"/>
-      <c r="Q25" s="188"/>
+      <c r="M25" s="150"/>
+      <c r="N25" s="151"/>
+      <c r="O25" s="149" t="s">
+        <v>290</v>
+      </c>
+      <c r="P25" s="150"/>
+      <c r="Q25" s="151"/>
       <c r="R25" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="S25" s="187" t="s">
-        <v>290</v>
-      </c>
-      <c r="T25" s="192"/>
-      <c r="U25" s="192"/>
-      <c r="V25" s="192"/>
-      <c r="W25" s="188"/>
+      <c r="S25" s="149" t="s">
+        <v>289</v>
+      </c>
+      <c r="T25" s="150"/>
+      <c r="U25" s="150"/>
+      <c r="V25" s="150"/>
+      <c r="W25" s="151"/>
       <c r="X25" s="122" t="s">
         <v>13</v>
       </c>
       <c r="Y25" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="Z25" s="187" t="s">
+      <c r="Z25" s="149" t="s">
         <v>14</v>
       </c>
-      <c r="AA25" s="192"/>
-      <c r="AB25" s="192"/>
-      <c r="AC25" s="188"/>
-      <c r="AD25" s="187" t="s">
+      <c r="AA25" s="150"/>
+      <c r="AB25" s="150"/>
+      <c r="AC25" s="151"/>
+      <c r="AD25" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="AE25" s="188"/>
+      <c r="AE25" s="151"/>
     </row>
     <row r="26" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="134"/>
@@ -7180,29 +7180,18 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="51">
-    <mergeCell ref="H20:AD20"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="Y12:AD12"/>
-    <mergeCell ref="Y14:AD14"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="H16:O16"/>
-    <mergeCell ref="Y16:AD16"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="S25:W25"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="A24:AE24"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="Y7:AD7"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="AB1:AE3"/>
+    <mergeCell ref="H1:AA1"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A5:AE5"/>
     <mergeCell ref="A10:AE10"/>
@@ -7219,18 +7208,29 @@
     <mergeCell ref="U12:X12"/>
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="W3:X3"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="Y7:AD7"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="AB1:AE3"/>
-    <mergeCell ref="H1:AA1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="A24:AE24"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H20:AD20"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="Y12:AD12"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="H16:O16"/>
+    <mergeCell ref="Y16:AD16"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="S25:W25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.35433070866141736" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -7281,14 +7281,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="227" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="D1" s="224" t="s">
+      <c r="B1" s="228"/>
+      <c r="D1" s="227" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="225"/>
+      <c r="E1" s="228"/>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8106,20 +8106,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="229" t="s">
+      <c r="A1" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="231"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="234"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="226" t="s">
+      <c r="A2" s="229" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="227"/>
-      <c r="C2" s="227"/>
-      <c r="D2" s="228"/>
+      <c r="B2" s="230"/>
+      <c r="C2" s="230"/>
+      <c r="D2" s="231"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -8186,12 +8186,12 @@
       <c r="D7" s="52"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="226" t="s">
+      <c r="A8" s="229" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="227"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="228"/>
+      <c r="B8" s="230"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="231"/>
     </row>
     <row r="9" spans="1:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
@@ -8258,12 +8258,12 @@
       <c r="H13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="226" t="s">
+      <c r="A14" s="229" t="s">
         <v>212</v>
       </c>
-      <c r="B14" s="227"/>
-      <c r="C14" s="227"/>
-      <c r="D14" s="228"/>
+      <c r="B14" s="230"/>
+      <c r="C14" s="230"/>
+      <c r="D14" s="231"/>
     </row>
     <row r="15" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
@@ -8824,10 +8824,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="232" t="s">
+      <c r="A1" s="235" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="232"/>
+      <c r="B1" s="235"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="22">
@@ -9252,19 +9252,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="236" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="235"/>
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
+      <c r="K1" s="238"/>
       <c r="L1" s="72"/>
       <c r="M1" s="72"/>
       <c r="N1" s="73"/>
